--- a/output/specyfikacja_wypelniona.xlsx
+++ b/output/specyfikacja_wypelniona.xlsx
@@ -225,7 +225,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -268,15 +268,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
@@ -1015,32 +1006,32 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="15" t="n">
+      <c r="A2" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="16" t="inlineStr">
+      <c r="B2" s="9" t="inlineStr">
         <is>
           <t>6104430000</t>
         </is>
       </c>
-      <c r="C2" s="15" t="n">
+      <c r="C2" s="1" t="n">
         <v>4118</v>
       </c>
-      <c r="D2" s="17" t="n">
+      <c r="D2" s="10" t="n">
         <v>1178.619</v>
       </c>
-      <c r="E2" s="17" t="n">
+      <c r="E2" s="10" t="n">
         <v>1234.796</v>
       </c>
-      <c r="F2" s="17" t="n">
+      <c r="F2" s="10" t="n">
         <v>15021.83</v>
       </c>
-      <c r="G2" s="15" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="H2" s="15" t="inlineStr">
+      <c r="G2" s="1" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H2" s="1" t="inlineStr">
         <is>
           <t>PCS</t>
         </is>
@@ -1050,12 +1041,12 @@
           <t>sukienka</t>
         </is>
       </c>
-      <c r="J2" s="15" t="inlineStr">
-        <is>
-          <t>CN</t>
-        </is>
-      </c>
-      <c r="K2" s="15" t="inlineStr">
+      <c r="J2" s="1" t="inlineStr">
+        <is>
+          <t>CN</t>
+        </is>
+      </c>
+      <c r="K2" s="1" t="inlineStr">
         <is>
           <t>100</t>
         </is>
@@ -1065,32 +1056,32 @@
       <c r="N2" s="5" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="15" t="n">
+      <c r="A3" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="18" t="inlineStr">
+      <c r="B3" s="9" t="inlineStr">
         <is>
           <t>6104530000</t>
         </is>
       </c>
-      <c r="C3" s="15" t="n">
+      <c r="C3" s="1" t="n">
         <v>111</v>
       </c>
-      <c r="D3" s="17" t="n">
+      <c r="D3" s="10" t="n">
         <v>25.724</v>
       </c>
-      <c r="E3" s="17" t="n">
+      <c r="E3" s="10" t="n">
         <v>27.106</v>
       </c>
-      <c r="F3" s="17" t="n">
+      <c r="F3" s="10" t="n">
         <v>362.83</v>
       </c>
-      <c r="G3" s="15" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="H3" s="15" t="inlineStr">
+      <c r="G3" s="1" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H3" s="1" t="inlineStr">
         <is>
           <t>PCS</t>
         </is>
@@ -1100,12 +1091,12 @@
           <t>spódnico-spodenki</t>
         </is>
       </c>
-      <c r="J3" s="15" t="inlineStr">
-        <is>
-          <t>CN</t>
-        </is>
-      </c>
-      <c r="K3" s="15" t="inlineStr">
+      <c r="J3" s="1" t="inlineStr">
+        <is>
+          <t>CN</t>
+        </is>
+      </c>
+      <c r="K3" s="1" t="inlineStr">
         <is>
           <t>100</t>
         </is>
@@ -1115,32 +1106,32 @@
       <c r="N3" s="5" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="15" t="n">
+      <c r="A4" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="18" t="inlineStr">
+      <c r="B4" s="9" t="inlineStr">
         <is>
           <t>6104230000</t>
         </is>
       </c>
-      <c r="C4" s="15" t="n">
+      <c r="C4" s="1" t="n">
         <v>367</v>
       </c>
-      <c r="D4" s="17" t="n">
+      <c r="D4" s="10" t="n">
         <v>107.033</v>
       </c>
-      <c r="E4" s="17" t="n">
+      <c r="E4" s="10" t="n">
         <v>111.871</v>
       </c>
-      <c r="F4" s="17" t="n">
+      <c r="F4" s="10" t="n">
         <v>1292.29</v>
       </c>
-      <c r="G4" s="15" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="H4" s="15" t="inlineStr">
+      <c r="G4" s="1" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H4" s="1" t="inlineStr">
         <is>
           <t>PCS</t>
         </is>
@@ -1150,12 +1141,12 @@
           <t>komplet</t>
         </is>
       </c>
-      <c r="J4" s="15" t="inlineStr">
-        <is>
-          <t>CN</t>
-        </is>
-      </c>
-      <c r="K4" s="15" t="inlineStr">
+      <c r="J4" s="1" t="inlineStr">
+        <is>
+          <t>CN</t>
+        </is>
+      </c>
+      <c r="K4" s="1" t="inlineStr">
         <is>
           <t>100</t>
         </is>
@@ -1165,32 +1156,32 @@
       <c r="N4" s="5" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="15" t="n">
+      <c r="A5" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="18" t="inlineStr">
+      <c r="B5" s="9" t="inlineStr">
         <is>
           <t>6115990000</t>
         </is>
       </c>
-      <c r="C5" s="15" t="n">
+      <c r="C5" s="1" t="n">
         <v>86</v>
       </c>
-      <c r="D5" s="17" t="n">
+      <c r="D5" s="10" t="n">
         <v>20.82</v>
       </c>
-      <c r="E5" s="17" t="n">
+      <c r="E5" s="10" t="n">
         <v>22.17</v>
       </c>
-      <c r="F5" s="17" t="n">
+      <c r="F5" s="10" t="n">
         <v>206.81</v>
       </c>
-      <c r="G5" s="15" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="H5" s="15" t="inlineStr">
+      <c r="G5" s="1" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H5" s="1" t="inlineStr">
         <is>
           <t>PCS</t>
         </is>
@@ -1200,12 +1191,12 @@
           <t>skarpetki</t>
         </is>
       </c>
-      <c r="J5" s="15" t="inlineStr">
-        <is>
-          <t>CN</t>
-        </is>
-      </c>
-      <c r="K5" s="15" t="inlineStr">
+      <c r="J5" s="1" t="inlineStr">
+        <is>
+          <t>CN</t>
+        </is>
+      </c>
+      <c r="K5" s="1" t="inlineStr">
         <is>
           <t>100</t>
         </is>
@@ -1215,32 +1206,32 @@
       <c r="N5" s="5" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="15" t="n">
+      <c r="A6" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="B6" s="18" t="inlineStr">
+      <c r="B6" s="9" t="inlineStr">
         <is>
           <t>3924900090</t>
         </is>
       </c>
-      <c r="C6" s="15" t="n">
+      <c r="C6" s="1" t="n">
         <v>335</v>
       </c>
-      <c r="D6" s="17" t="n">
+      <c r="D6" s="10" t="n">
         <v>52.975</v>
       </c>
-      <c r="E6" s="17" t="n">
+      <c r="E6" s="10" t="n">
         <v>56.435</v>
       </c>
-      <c r="F6" s="17" t="n">
+      <c r="F6" s="10" t="n">
         <v>484.74</v>
       </c>
-      <c r="G6" s="15" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="H6" s="15" t="inlineStr">
+      <c r="G6" s="1" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H6" s="1" t="inlineStr">
         <is>
           <t>PCS</t>
         </is>
@@ -1250,12 +1241,12 @@
           <t>stojak kuchenny</t>
         </is>
       </c>
-      <c r="J6" s="15" t="inlineStr">
-        <is>
-          <t>CN</t>
-        </is>
-      </c>
-      <c r="K6" s="15" t="inlineStr">
+      <c r="J6" s="1" t="inlineStr">
+        <is>
+          <t>CN</t>
+        </is>
+      </c>
+      <c r="K6" s="1" t="inlineStr">
         <is>
           <t>100</t>
         </is>
@@ -1265,32 +1256,32 @@
       <c r="N6" s="5" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="15" t="n">
+      <c r="A7" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="B7" s="18" t="inlineStr">
+      <c r="B7" s="9" t="inlineStr">
         <is>
           <t>6307909899</t>
         </is>
       </c>
-      <c r="C7" s="15" t="n">
+      <c r="C7" s="1" t="n">
         <v>268</v>
       </c>
-      <c r="D7" s="17" t="n">
+      <c r="D7" s="10" t="n">
         <v>27.497</v>
       </c>
-      <c r="E7" s="17" t="n">
+      <c r="E7" s="10" t="n">
         <v>29.999</v>
       </c>
-      <c r="F7" s="17" t="n">
+      <c r="F7" s="10" t="n">
         <v>494.74</v>
       </c>
-      <c r="G7" s="15" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="H7" s="15" t="inlineStr">
+      <c r="G7" s="1" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H7" s="1" t="inlineStr">
         <is>
           <t>PCS</t>
         </is>
@@ -1300,12 +1291,12 @@
           <t>rekwizyt</t>
         </is>
       </c>
-      <c r="J7" s="15" t="inlineStr">
-        <is>
-          <t>CN</t>
-        </is>
-      </c>
-      <c r="K7" s="15" t="inlineStr">
+      <c r="J7" s="1" t="inlineStr">
+        <is>
+          <t>CN</t>
+        </is>
+      </c>
+      <c r="K7" s="1" t="inlineStr">
         <is>
           <t>100</t>
         </is>
@@ -1315,32 +1306,32 @@
       <c r="N7" s="5" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="15" t="n">
+      <c r="A8" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="B8" s="18" t="inlineStr">
+      <c r="B8" s="9" t="inlineStr">
         <is>
           <t>6307901000</t>
         </is>
       </c>
-      <c r="C8" s="15" t="n">
+      <c r="C8" s="1" t="n">
         <v>450</v>
       </c>
-      <c r="D8" s="17" t="n">
+      <c r="D8" s="10" t="n">
         <v>64.961</v>
       </c>
-      <c r="E8" s="17" t="n">
+      <c r="E8" s="10" t="n">
         <v>70.471</v>
       </c>
-      <c r="F8" s="17" t="n">
+      <c r="F8" s="10" t="n">
         <v>744.55</v>
       </c>
-      <c r="G8" s="15" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="H8" s="15" t="inlineStr">
+      <c r="G8" s="1" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H8" s="1" t="inlineStr">
         <is>
           <t>PCS</t>
         </is>
@@ -1350,12 +1341,12 @@
           <t>kosz do przechowywania</t>
         </is>
       </c>
-      <c r="J8" s="15" t="inlineStr">
-        <is>
-          <t>CN</t>
-        </is>
-      </c>
-      <c r="K8" s="15" t="inlineStr">
+      <c r="J8" s="1" t="inlineStr">
+        <is>
+          <t>CN</t>
+        </is>
+      </c>
+      <c r="K8" s="1" t="inlineStr">
         <is>
           <t>100</t>
         </is>
@@ -1365,32 +1356,32 @@
       <c r="N8" s="5" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="15" t="n">
+      <c r="A9" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="B9" s="18" t="inlineStr">
+      <c r="B9" s="9" t="inlineStr">
         <is>
           <t>6302539000</t>
         </is>
       </c>
-      <c r="C9" s="15" t="n">
+      <c r="C9" s="1" t="n">
         <v>180</v>
       </c>
-      <c r="D9" s="17" t="n">
+      <c r="D9" s="10" t="n">
         <v>61.59</v>
       </c>
-      <c r="E9" s="17" t="n">
+      <c r="E9" s="10" t="n">
         <v>64.05</v>
       </c>
-      <c r="F9" s="17" t="n">
+      <c r="F9" s="10" t="n">
         <v>448.09</v>
       </c>
-      <c r="G9" s="15" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="H9" s="15" t="inlineStr">
+      <c r="G9" s="1" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H9" s="1" t="inlineStr">
         <is>
           <t>PCS</t>
         </is>
@@ -1400,12 +1391,12 @@
           <t>obrus</t>
         </is>
       </c>
-      <c r="J9" s="15" t="inlineStr">
-        <is>
-          <t>CN</t>
-        </is>
-      </c>
-      <c r="K9" s="15" t="inlineStr">
+      <c r="J9" s="1" t="inlineStr">
+        <is>
+          <t>CN</t>
+        </is>
+      </c>
+      <c r="K9" s="1" t="inlineStr">
         <is>
           <t>100</t>
         </is>
@@ -1415,32 +1406,32 @@
       <c r="N9" s="5" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="15" t="n">
+      <c r="A10" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="B10" s="18" t="inlineStr">
+      <c r="B10" s="9" t="inlineStr">
         <is>
           <t>6108320000</t>
         </is>
       </c>
-      <c r="C10" s="15" t="n">
+      <c r="C10" s="1" t="n">
         <v>432</v>
       </c>
-      <c r="D10" s="17" t="n">
+      <c r="D10" s="10" t="n">
         <v>91.521</v>
       </c>
-      <c r="E10" s="17" t="n">
+      <c r="E10" s="10" t="n">
         <v>96.261</v>
       </c>
-      <c r="F10" s="17" t="n">
+      <c r="F10" s="10" t="n">
         <v>1290.68</v>
       </c>
-      <c r="G10" s="15" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="H10" s="15" t="inlineStr">
+      <c r="G10" s="1" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H10" s="1" t="inlineStr">
         <is>
           <t>PCS</t>
         </is>
@@ -1450,12 +1441,12 @@
           <t>piżama</t>
         </is>
       </c>
-      <c r="J10" s="15" t="inlineStr">
-        <is>
-          <t>CN</t>
-        </is>
-      </c>
-      <c r="K10" s="15" t="inlineStr">
+      <c r="J10" s="1" t="inlineStr">
+        <is>
+          <t>CN</t>
+        </is>
+      </c>
+      <c r="K10" s="1" t="inlineStr">
         <is>
           <t>100</t>
         </is>
@@ -1465,32 +1456,32 @@
       <c r="N10" s="5" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="15" t="n">
+      <c r="A11" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="B11" s="18" t="inlineStr">
+      <c r="B11" s="9" t="inlineStr">
         <is>
           <t>6114300000</t>
         </is>
       </c>
-      <c r="C11" s="15" t="n">
+      <c r="C11" s="1" t="n">
         <v>2695</v>
       </c>
-      <c r="D11" s="17" t="n">
+      <c r="D11" s="10" t="n">
         <v>361.178</v>
       </c>
-      <c r="E11" s="17" t="n">
+      <c r="E11" s="10" t="n">
         <v>380.177</v>
       </c>
-      <c r="F11" s="17" t="n">
+      <c r="F11" s="10" t="n">
         <v>6862.86</v>
       </c>
-      <c r="G11" s="15" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="H11" s="15" t="inlineStr">
+      <c r="G11" s="1" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H11" s="1" t="inlineStr">
         <is>
           <t>PCS</t>
         </is>
@@ -1500,12 +1491,12 @@
           <t>topy damskie</t>
         </is>
       </c>
-      <c r="J11" s="15" t="inlineStr">
-        <is>
-          <t>CN</t>
-        </is>
-      </c>
-      <c r="K11" s="15" t="inlineStr">
+      <c r="J11" s="1" t="inlineStr">
+        <is>
+          <t>CN</t>
+        </is>
+      </c>
+      <c r="K11" s="1" t="inlineStr">
         <is>
           <t>100</t>
         </is>
@@ -1515,32 +1506,32 @@
       <c r="N11" s="5" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="15" t="n">
+      <c r="A12" s="1" t="n">
         <v>11</v>
       </c>
-      <c r="B12" s="18" t="inlineStr">
+      <c r="B12" s="9" t="inlineStr">
         <is>
           <t>6402999800</t>
         </is>
       </c>
-      <c r="C12" s="15" t="n">
+      <c r="C12" s="1" t="n">
         <v>59</v>
       </c>
-      <c r="D12" s="17" t="n">
+      <c r="D12" s="10" t="n">
         <v>20.508</v>
       </c>
-      <c r="E12" s="17" t="n">
+      <c r="E12" s="10" t="n">
         <v>22.544</v>
       </c>
-      <c r="F12" s="17" t="n">
+      <c r="F12" s="10" t="n">
         <v>165.73</v>
       </c>
-      <c r="G12" s="15" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="H12" s="15" t="inlineStr">
+      <c r="G12" s="1" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H12" s="1" t="inlineStr">
         <is>
           <t>PCS</t>
         </is>
@@ -1550,12 +1541,12 @@
           <t>obuwie damskie</t>
         </is>
       </c>
-      <c r="J12" s="15" t="inlineStr">
-        <is>
-          <t>CN</t>
-        </is>
-      </c>
-      <c r="K12" s="15" t="inlineStr">
+      <c r="J12" s="1" t="inlineStr">
+        <is>
+          <t>CN</t>
+        </is>
+      </c>
+      <c r="K12" s="1" t="inlineStr">
         <is>
           <t>100</t>
         </is>
@@ -1565,32 +1556,32 @@
       <c r="N12" s="5" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="15" t="n">
+      <c r="A13" s="1" t="n">
         <v>12</v>
       </c>
-      <c r="B13" s="18" t="inlineStr">
+      <c r="B13" s="9" t="inlineStr">
         <is>
           <t>6402993100</t>
         </is>
       </c>
-      <c r="C13" s="15" t="n">
+      <c r="C13" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="D13" s="17" t="n">
+      <c r="D13" s="10" t="n">
         <v>4.634</v>
       </c>
-      <c r="E13" s="17" t="n">
+      <c r="E13" s="10" t="n">
         <v>5.089</v>
       </c>
-      <c r="F13" s="17" t="n">
+      <c r="F13" s="10" t="n">
         <v>32.62</v>
       </c>
-      <c r="G13" s="15" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="H13" s="15" t="inlineStr">
+      <c r="G13" s="1" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H13" s="1" t="inlineStr">
         <is>
           <t>PCS</t>
         </is>
@@ -1600,12 +1591,12 @@
           <t>sandały</t>
         </is>
       </c>
-      <c r="J13" s="15" t="inlineStr">
-        <is>
-          <t>CN</t>
-        </is>
-      </c>
-      <c r="K13" s="15" t="inlineStr">
+      <c r="J13" s="1" t="inlineStr">
+        <is>
+          <t>CN</t>
+        </is>
+      </c>
+      <c r="K13" s="1" t="inlineStr">
         <is>
           <t>100</t>
         </is>
@@ -1615,32 +1606,32 @@
       <c r="N13" s="5" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="15" t="n">
+      <c r="A14" s="1" t="n">
         <v>13</v>
       </c>
-      <c r="B14" s="18" t="inlineStr">
+      <c r="B14" s="9" t="inlineStr">
         <is>
           <t>6211439000</t>
         </is>
       </c>
-      <c r="C14" s="15" t="n">
+      <c r="C14" s="1" t="n">
         <v>560</v>
       </c>
-      <c r="D14" s="17" t="n">
+      <c r="D14" s="10" t="n">
         <v>128.578</v>
       </c>
-      <c r="E14" s="17" t="n">
+      <c r="E14" s="10" t="n">
         <v>135.759</v>
       </c>
-      <c r="F14" s="17" t="n">
+      <c r="F14" s="10" t="n">
         <v>2100.2</v>
       </c>
-      <c r="G14" s="15" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="H14" s="15" t="inlineStr">
+      <c r="G14" s="1" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H14" s="1" t="inlineStr">
         <is>
           <t>PCS</t>
         </is>
@@ -1650,12 +1641,12 @@
           <t>topy damskie</t>
         </is>
       </c>
-      <c r="J14" s="15" t="inlineStr">
-        <is>
-          <t>CN</t>
-        </is>
-      </c>
-      <c r="K14" s="15" t="inlineStr">
+      <c r="J14" s="1" t="inlineStr">
+        <is>
+          <t>CN</t>
+        </is>
+      </c>
+      <c r="K14" s="1" t="inlineStr">
         <is>
           <t>100</t>
         </is>
@@ -1665,32 +1656,32 @@
       <c r="N14" s="5" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="15" t="n">
+      <c r="A15" s="1" t="n">
         <v>14</v>
       </c>
-      <c r="B15" s="18" t="inlineStr">
+      <c r="B15" s="9" t="inlineStr">
         <is>
           <t>6206400000</t>
         </is>
       </c>
-      <c r="C15" s="15" t="n">
+      <c r="C15" s="1" t="n">
         <v>3097</v>
       </c>
-      <c r="D15" s="17" t="n">
+      <c r="D15" s="10" t="n">
         <v>530.189</v>
       </c>
-      <c r="E15" s="17" t="n">
+      <c r="E15" s="10" t="n">
         <v>558.384</v>
       </c>
-      <c r="F15" s="17" t="n">
+      <c r="F15" s="10" t="n">
         <v>10681.48</v>
       </c>
-      <c r="G15" s="15" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="H15" s="15" t="inlineStr">
+      <c r="G15" s="1" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H15" s="1" t="inlineStr">
         <is>
           <t>PCS</t>
         </is>
@@ -1700,12 +1691,12 @@
           <t>bluzka</t>
         </is>
       </c>
-      <c r="J15" s="15" t="inlineStr">
-        <is>
-          <t>CN</t>
-        </is>
-      </c>
-      <c r="K15" s="15" t="inlineStr">
+      <c r="J15" s="1" t="inlineStr">
+        <is>
+          <t>CN</t>
+        </is>
+      </c>
+      <c r="K15" s="1" t="inlineStr">
         <is>
           <t>100</t>
         </is>
@@ -1715,32 +1706,32 @@
       <c r="N15" s="5" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="15" t="n">
+      <c r="A16" s="1" t="n">
         <v>15</v>
       </c>
-      <c r="B16" s="18" t="inlineStr">
+      <c r="B16" s="9" t="inlineStr">
         <is>
           <t>6402995000</t>
         </is>
       </c>
-      <c r="C16" s="15" t="n">
-        <v>100</v>
-      </c>
-      <c r="D16" s="17" t="n">
+      <c r="C16" s="1" t="n">
+        <v>100</v>
+      </c>
+      <c r="D16" s="10" t="n">
         <v>10.586</v>
       </c>
-      <c r="E16" s="17" t="n">
+      <c r="E16" s="10" t="n">
         <v>13.169</v>
       </c>
-      <c r="F16" s="17" t="n">
+      <c r="F16" s="10" t="n">
         <v>142.88</v>
       </c>
-      <c r="G16" s="15" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="H16" s="15" t="inlineStr">
+      <c r="G16" s="1" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H16" s="1" t="inlineStr">
         <is>
           <t>PCS</t>
         </is>
@@ -1750,12 +1741,12 @@
           <t>kapcie</t>
         </is>
       </c>
-      <c r="J16" s="15" t="inlineStr">
-        <is>
-          <t>CN</t>
-        </is>
-      </c>
-      <c r="K16" s="15" t="inlineStr">
+      <c r="J16" s="1" t="inlineStr">
+        <is>
+          <t>CN</t>
+        </is>
+      </c>
+      <c r="K16" s="1" t="inlineStr">
         <is>
           <t>100</t>
         </is>
@@ -1765,32 +1756,32 @@
       <c r="N16" s="5" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="15" t="n">
+      <c r="A17" s="1" t="n">
         <v>16</v>
       </c>
-      <c r="B17" s="18" t="inlineStr">
+      <c r="B17" s="9" t="inlineStr">
         <is>
           <t>6212109000</t>
         </is>
       </c>
-      <c r="C17" s="15" t="n">
+      <c r="C17" s="1" t="n">
         <v>3507</v>
       </c>
-      <c r="D17" s="17" t="n">
+      <c r="D17" s="10" t="n">
         <v>445.411</v>
       </c>
-      <c r="E17" s="17" t="n">
+      <c r="E17" s="10" t="n">
         <v>479.998</v>
       </c>
-      <c r="F17" s="17" t="n">
+      <c r="F17" s="10" t="n">
         <v>9750.129999999999</v>
       </c>
-      <c r="G17" s="15" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="H17" s="15" t="inlineStr">
+      <c r="G17" s="1" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H17" s="1" t="inlineStr">
         <is>
           <t>PCS</t>
         </is>
@@ -1800,12 +1791,12 @@
           <t>biustonosz</t>
         </is>
       </c>
-      <c r="J17" s="15" t="inlineStr">
-        <is>
-          <t>CN</t>
-        </is>
-      </c>
-      <c r="K17" s="15" t="inlineStr">
+      <c r="J17" s="1" t="inlineStr">
+        <is>
+          <t>CN</t>
+        </is>
+      </c>
+      <c r="K17" s="1" t="inlineStr">
         <is>
           <t>100</t>
         </is>
@@ -1815,32 +1806,32 @@
       <c r="N17" s="5" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="15" t="n">
+      <c r="A18" s="1" t="n">
         <v>17</v>
       </c>
-      <c r="B18" s="18" t="inlineStr">
+      <c r="B18" s="9" t="inlineStr">
         <is>
           <t>6109902000</t>
         </is>
       </c>
-      <c r="C18" s="15" t="n">
+      <c r="C18" s="1" t="n">
         <v>806</v>
       </c>
-      <c r="D18" s="17" t="n">
+      <c r="D18" s="10" t="n">
         <v>131.578</v>
       </c>
-      <c r="E18" s="17" t="n">
+      <c r="E18" s="10" t="n">
         <v>137.586</v>
       </c>
-      <c r="F18" s="17" t="n">
+      <c r="F18" s="10" t="n">
         <v>1833.03</v>
       </c>
-      <c r="G18" s="15" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="H18" s="15" t="inlineStr">
+      <c r="G18" s="1" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H18" s="1" t="inlineStr">
         <is>
           <t>PCS</t>
         </is>
@@ -1850,12 +1841,12 @@
           <t>topy damskie</t>
         </is>
       </c>
-      <c r="J18" s="15" t="inlineStr">
-        <is>
-          <t>CN</t>
-        </is>
-      </c>
-      <c r="K18" s="15" t="inlineStr">
+      <c r="J18" s="1" t="inlineStr">
+        <is>
+          <t>CN</t>
+        </is>
+      </c>
+      <c r="K18" s="1" t="inlineStr">
         <is>
           <t>100</t>
         </is>
@@ -1865,32 +1856,32 @@
       <c r="N18" s="5" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="15" t="n">
+      <c r="A19" s="1" t="n">
         <v>18</v>
       </c>
-      <c r="B19" s="18" t="inlineStr">
+      <c r="B19" s="9" t="inlineStr">
         <is>
           <t>6111309000</t>
         </is>
       </c>
-      <c r="C19" s="15" t="n">
+      <c r="C19" s="1" t="n">
         <v>155</v>
       </c>
-      <c r="D19" s="17" t="n">
+      <c r="D19" s="10" t="n">
         <v>12.632</v>
       </c>
-      <c r="E19" s="17" t="n">
+      <c r="E19" s="10" t="n">
         <v>13.552</v>
       </c>
-      <c r="F19" s="17" t="n">
+      <c r="F19" s="10" t="n">
         <v>279.03</v>
       </c>
-      <c r="G19" s="15" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="H19" s="15" t="inlineStr">
+      <c r="G19" s="1" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H19" s="1" t="inlineStr">
         <is>
           <t>PCS</t>
         </is>
@@ -1900,12 +1891,12 @@
           <t>komplet</t>
         </is>
       </c>
-      <c r="J19" s="15" t="inlineStr">
-        <is>
-          <t>CN</t>
-        </is>
-      </c>
-      <c r="K19" s="15" t="inlineStr">
+      <c r="J19" s="1" t="inlineStr">
+        <is>
+          <t>CN</t>
+        </is>
+      </c>
+      <c r="K19" s="1" t="inlineStr">
         <is>
           <t>100</t>
         </is>
@@ -1914,33 +1905,33 @@
       <c r="M19" s="5" t="n"/>
       <c r="N19" s="5" t="n"/>
     </row>
-    <row r="20" customFormat="1" s="4">
-      <c r="A20" s="15" t="n">
+    <row r="20">
+      <c r="A20" s="1" t="n">
         <v>19</v>
       </c>
-      <c r="B20" s="18" t="inlineStr">
+      <c r="B20" s="9" t="inlineStr">
         <is>
           <t>6505009090</t>
         </is>
       </c>
-      <c r="C20" s="15" t="n">
+      <c r="C20" s="1" t="n">
         <v>92</v>
       </c>
-      <c r="D20" s="17" t="n">
+      <c r="D20" s="10" t="n">
         <v>4.434</v>
       </c>
-      <c r="E20" s="17" t="n">
+      <c r="E20" s="10" t="n">
         <v>4.777</v>
       </c>
-      <c r="F20" s="17" t="n">
+      <c r="F20" s="10" t="n">
         <v>74.3</v>
       </c>
-      <c r="G20" s="15" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="H20" s="15" t="inlineStr">
+      <c r="G20" s="1" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H20" s="1" t="inlineStr">
         <is>
           <t>PCS</t>
         </is>
@@ -1950,12 +1941,12 @@
           <t>kapelusz</t>
         </is>
       </c>
-      <c r="J20" s="15" t="inlineStr">
-        <is>
-          <t>CN</t>
-        </is>
-      </c>
-      <c r="K20" s="15" t="inlineStr">
+      <c r="J20" s="1" t="inlineStr">
+        <is>
+          <t>CN</t>
+        </is>
+      </c>
+      <c r="K20" s="1" t="inlineStr">
         <is>
           <t>100</t>
         </is>
@@ -1965,32 +1956,32 @@
       <c r="N20" s="5" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="15" t="n">
+      <c r="A21" s="1" t="n">
         <v>20</v>
       </c>
-      <c r="B21" s="18" t="inlineStr">
+      <c r="B21" s="9" t="inlineStr">
         <is>
           <t>6204238000</t>
         </is>
       </c>
-      <c r="C21" s="15" t="n">
+      <c r="C21" s="1" t="n">
         <v>371</v>
       </c>
-      <c r="D21" s="17" t="n">
+      <c r="D21" s="10" t="n">
         <v>117.292</v>
       </c>
-      <c r="E21" s="17" t="n">
+      <c r="E21" s="10" t="n">
         <v>122.15</v>
       </c>
-      <c r="F21" s="17" t="n">
+      <c r="F21" s="10" t="n">
         <v>1664.93</v>
       </c>
-      <c r="G21" s="15" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="H21" s="15" t="inlineStr">
+      <c r="G21" s="1" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H21" s="1" t="inlineStr">
         <is>
           <t>PCS</t>
         </is>
@@ -2000,12 +1991,12 @@
           <t>komplet</t>
         </is>
       </c>
-      <c r="J21" s="15" t="inlineStr">
-        <is>
-          <t>CN</t>
-        </is>
-      </c>
-      <c r="K21" s="15" t="inlineStr">
+      <c r="J21" s="1" t="inlineStr">
+        <is>
+          <t>CN</t>
+        </is>
+      </c>
+      <c r="K21" s="1" t="inlineStr">
         <is>
           <t>100</t>
         </is>
@@ -2015,32 +2006,32 @@
       <c r="N21" s="5" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="15" t="n">
+      <c r="A22" s="1" t="n">
         <v>21</v>
       </c>
-      <c r="B22" s="18" t="inlineStr">
+      <c r="B22" s="9" t="inlineStr">
         <is>
           <t>6212101000</t>
         </is>
       </c>
-      <c r="C22" s="15" t="n">
+      <c r="C22" s="1" t="n">
         <v>65</v>
       </c>
-      <c r="D22" s="17" t="n">
+      <c r="D22" s="10" t="n">
         <v>4.705</v>
       </c>
-      <c r="E22" s="17" t="n">
+      <c r="E22" s="10" t="n">
         <v>5.392</v>
       </c>
-      <c r="F22" s="17" t="n">
+      <c r="F22" s="10" t="n">
         <v>181.95</v>
       </c>
-      <c r="G22" s="15" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="H22" s="15" t="inlineStr">
+      <c r="G22" s="1" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H22" s="1" t="inlineStr">
         <is>
           <t>PCS</t>
         </is>
@@ -2050,12 +2041,12 @@
           <t>komplet bielizny</t>
         </is>
       </c>
-      <c r="J22" s="15" t="inlineStr">
-        <is>
-          <t>CN</t>
-        </is>
-      </c>
-      <c r="K22" s="15" t="inlineStr">
+      <c r="J22" s="1" t="inlineStr">
+        <is>
+          <t>CN</t>
+        </is>
+      </c>
+      <c r="K22" s="1" t="inlineStr">
         <is>
           <t>100</t>
         </is>
@@ -2065,32 +2056,32 @@
       <c r="N22" s="5" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="15" t="n">
+      <c r="A23" s="1" t="n">
         <v>22</v>
       </c>
-      <c r="B23" s="18" t="inlineStr">
+      <c r="B23" s="9" t="inlineStr">
         <is>
           <t>6112419000</t>
         </is>
       </c>
-      <c r="C23" s="15" t="n">
+      <c r="C23" s="1" t="n">
         <v>4149</v>
       </c>
-      <c r="D23" s="17" t="n">
+      <c r="D23" s="10" t="n">
         <v>672.1420000000001</v>
       </c>
-      <c r="E23" s="17" t="n">
+      <c r="E23" s="10" t="n">
         <v>705.711</v>
       </c>
-      <c r="F23" s="17" t="n">
+      <c r="F23" s="10" t="n">
         <v>12213.81</v>
       </c>
-      <c r="G23" s="15" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="H23" s="15" t="inlineStr">
+      <c r="G23" s="1" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H23" s="1" t="inlineStr">
         <is>
           <t>PCS</t>
         </is>
@@ -2100,12 +2091,12 @@
           <t>topy damskie</t>
         </is>
       </c>
-      <c r="J23" s="15" t="inlineStr">
-        <is>
-          <t>CN</t>
-        </is>
-      </c>
-      <c r="K23" s="15" t="inlineStr">
+      <c r="J23" s="1" t="inlineStr">
+        <is>
+          <t>CN</t>
+        </is>
+      </c>
+      <c r="K23" s="1" t="inlineStr">
         <is>
           <t>100</t>
         </is>
@@ -2115,32 +2106,32 @@
       <c r="N23" s="5" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="15" t="n">
+      <c r="A24" s="1" t="n">
         <v>23</v>
       </c>
-      <c r="B24" s="18" t="inlineStr">
+      <c r="B24" s="9" t="inlineStr">
         <is>
           <t>6203439000</t>
         </is>
       </c>
-      <c r="C24" s="15" t="n">
+      <c r="C24" s="1" t="n">
         <v>135</v>
       </c>
-      <c r="D24" s="17" t="n">
+      <c r="D24" s="10" t="n">
         <v>29.812</v>
       </c>
-      <c r="E24" s="17" t="n">
+      <c r="E24" s="10" t="n">
         <v>31.722</v>
       </c>
-      <c r="F24" s="17" t="n">
+      <c r="F24" s="10" t="n">
         <v>416.61</v>
       </c>
-      <c r="G24" s="15" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="H24" s="15" t="inlineStr">
+      <c r="G24" s="1" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H24" s="1" t="inlineStr">
         <is>
           <t>PCS</t>
         </is>
@@ -2150,12 +2141,12 @@
           <t>spodenki</t>
         </is>
       </c>
-      <c r="J24" s="15" t="inlineStr">
-        <is>
-          <t>CN</t>
-        </is>
-      </c>
-      <c r="K24" s="15" t="inlineStr">
+      <c r="J24" s="1" t="inlineStr">
+        <is>
+          <t>CN</t>
+        </is>
+      </c>
+      <c r="K24" s="1" t="inlineStr">
         <is>
           <t>100</t>
         </is>
@@ -2165,32 +2156,32 @@
       <c r="N24" s="5" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="15" t="n">
+      <c r="A25" s="1" t="n">
         <v>24</v>
       </c>
-      <c r="B25" s="18" t="inlineStr">
+      <c r="B25" s="9" t="inlineStr">
         <is>
           <t>6209200090</t>
         </is>
       </c>
-      <c r="C25" s="15" t="n">
+      <c r="C25" s="1" t="n">
         <v>118</v>
       </c>
-      <c r="D25" s="17" t="n">
+      <c r="D25" s="10" t="n">
         <v>9.481999999999999</v>
       </c>
-      <c r="E25" s="17" t="n">
+      <c r="E25" s="10" t="n">
         <v>10.351</v>
       </c>
-      <c r="F25" s="17" t="n">
+      <c r="F25" s="10" t="n">
         <v>322.3</v>
       </c>
-      <c r="G25" s="15" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="H25" s="15" t="inlineStr">
+      <c r="G25" s="1" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H25" s="1" t="inlineStr">
         <is>
           <t>PCS</t>
         </is>
@@ -2200,12 +2191,12 @@
           <t>komplet</t>
         </is>
       </c>
-      <c r="J25" s="15" t="inlineStr">
-        <is>
-          <t>CN</t>
-        </is>
-      </c>
-      <c r="K25" s="15" t="inlineStr">
+      <c r="J25" s="1" t="inlineStr">
+        <is>
+          <t>CN</t>
+        </is>
+      </c>
+      <c r="K25" s="1" t="inlineStr">
         <is>
           <t>100</t>
         </is>
@@ -2215,32 +2206,32 @@
       <c r="N25" s="5" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="15" t="n">
+      <c r="A26" s="1" t="n">
         <v>25</v>
       </c>
-      <c r="B26" s="18" t="inlineStr">
+      <c r="B26" s="9" t="inlineStr">
         <is>
           <t>6211110000</t>
         </is>
       </c>
-      <c r="C26" s="15" t="n">
+      <c r="C26" s="1" t="n">
         <v>29</v>
       </c>
-      <c r="D26" s="17" t="n">
+      <c r="D26" s="10" t="n">
         <v>3.116</v>
       </c>
-      <c r="E26" s="17" t="n">
+      <c r="E26" s="10" t="n">
         <v>3.476</v>
       </c>
-      <c r="F26" s="17" t="n">
+      <c r="F26" s="10" t="n">
         <v>75.98</v>
       </c>
-      <c r="G26" s="15" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="H26" s="15" t="inlineStr">
+      <c r="G26" s="1" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H26" s="1" t="inlineStr">
         <is>
           <t>PCS</t>
         </is>
@@ -2250,12 +2241,12 @@
           <t>dół stroju kąpielowego</t>
         </is>
       </c>
-      <c r="J26" s="15" t="inlineStr">
-        <is>
-          <t>CN</t>
-        </is>
-      </c>
-      <c r="K26" s="15" t="inlineStr">
+      <c r="J26" s="1" t="inlineStr">
+        <is>
+          <t>CN</t>
+        </is>
+      </c>
+      <c r="K26" s="1" t="inlineStr">
         <is>
           <t>100</t>
         </is>
@@ -2265,32 +2256,32 @@
       <c r="N26" s="5" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="15" t="n">
+      <c r="A27" s="1" t="n">
         <v>26</v>
       </c>
-      <c r="B27" s="18" t="inlineStr">
+      <c r="B27" s="9" t="inlineStr">
         <is>
           <t>6209300090</t>
         </is>
       </c>
-      <c r="C27" s="15" t="n">
+      <c r="C27" s="1" t="n">
         <v>93</v>
       </c>
-      <c r="D27" s="17" t="n">
+      <c r="D27" s="10" t="n">
         <v>5.629</v>
       </c>
-      <c r="E27" s="17" t="n">
+      <c r="E27" s="10" t="n">
         <v>6.193</v>
       </c>
-      <c r="F27" s="17" t="n">
+      <c r="F27" s="10" t="n">
         <v>196.14</v>
       </c>
-      <c r="G27" s="15" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="H27" s="15" t="inlineStr">
+      <c r="G27" s="1" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H27" s="1" t="inlineStr">
         <is>
           <t>PCS</t>
         </is>
@@ -2300,12 +2291,12 @@
           <t>komplet</t>
         </is>
       </c>
-      <c r="J27" s="15" t="inlineStr">
-        <is>
-          <t>CN</t>
-        </is>
-      </c>
-      <c r="K27" s="15" t="inlineStr">
+      <c r="J27" s="1" t="inlineStr">
+        <is>
+          <t>CN</t>
+        </is>
+      </c>
+      <c r="K27" s="1" t="inlineStr">
         <is>
           <t>100</t>
         </is>
@@ -2315,32 +2306,32 @@
       <c r="N27" s="5" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="15" t="n">
+      <c r="A28" s="1" t="n">
         <v>27</v>
       </c>
-      <c r="B28" s="18" t="inlineStr">
+      <c r="B28" s="9" t="inlineStr">
         <is>
           <t>6104630000</t>
         </is>
       </c>
-      <c r="C28" s="15" t="n">
+      <c r="C28" s="1" t="n">
         <v>192</v>
       </c>
-      <c r="D28" s="17" t="n">
+      <c r="D28" s="10" t="n">
         <v>38.15</v>
       </c>
-      <c r="E28" s="17" t="n">
+      <c r="E28" s="10" t="n">
         <v>39.95</v>
       </c>
-      <c r="F28" s="17" t="n">
+      <c r="F28" s="10" t="n">
         <v>486.04</v>
       </c>
-      <c r="G28" s="15" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="H28" s="15" t="inlineStr">
+      <c r="G28" s="1" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H28" s="1" t="inlineStr">
         <is>
           <t>PCS</t>
         </is>
@@ -2350,12 +2341,12 @@
           <t>spodenki</t>
         </is>
       </c>
-      <c r="J28" s="15" t="inlineStr">
-        <is>
-          <t>CN</t>
-        </is>
-      </c>
-      <c r="K28" s="15" t="inlineStr">
+      <c r="J28" s="1" t="inlineStr">
+        <is>
+          <t>CN</t>
+        </is>
+      </c>
+      <c r="K28" s="1" t="inlineStr">
         <is>
           <t>100</t>
         </is>
@@ -2365,32 +2356,32 @@
       <c r="N28" s="5" t="n"/>
     </row>
     <row r="29">
-      <c r="A29" s="15" t="n">
+      <c r="A29" s="1" t="n">
         <v>28</v>
       </c>
-      <c r="B29" s="18" t="inlineStr">
+      <c r="B29" s="9" t="inlineStr">
         <is>
           <t>6106200000</t>
         </is>
       </c>
-      <c r="C29" s="15" t="n">
+      <c r="C29" s="1" t="n">
         <v>12</v>
       </c>
-      <c r="D29" s="17" t="n">
+      <c r="D29" s="10" t="n">
         <v>1.996</v>
       </c>
-      <c r="E29" s="17" t="n">
+      <c r="E29" s="10" t="n">
         <v>2.122</v>
       </c>
-      <c r="F29" s="17" t="n">
+      <c r="F29" s="10" t="n">
         <v>27.6</v>
       </c>
-      <c r="G29" s="15" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="H29" s="15" t="inlineStr">
+      <c r="G29" s="1" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H29" s="1" t="inlineStr">
         <is>
           <t>PCS</t>
         </is>
@@ -2400,12 +2391,12 @@
           <t>bluzka</t>
         </is>
       </c>
-      <c r="J29" s="15" t="inlineStr">
-        <is>
-          <t>CN</t>
-        </is>
-      </c>
-      <c r="K29" s="15" t="inlineStr">
+      <c r="J29" s="1" t="inlineStr">
+        <is>
+          <t>CN</t>
+        </is>
+      </c>
+      <c r="K29" s="1" t="inlineStr">
         <is>
           <t>100</t>
         </is>
@@ -2415,32 +2406,32 @@
       <c r="N29" s="5" t="n"/>
     </row>
     <row r="30">
-      <c r="A30" s="15" t="n">
+      <c r="A30" s="1" t="n">
         <v>29</v>
       </c>
-      <c r="B30" s="18" t="inlineStr">
+      <c r="B30" s="9" t="inlineStr">
         <is>
           <t>6204623990</t>
         </is>
       </c>
-      <c r="C30" s="15" t="n">
+      <c r="C30" s="1" t="n">
         <v>168</v>
       </c>
-      <c r="D30" s="17" t="n">
+      <c r="D30" s="10" t="n">
         <v>47.914</v>
       </c>
-      <c r="E30" s="17" t="n">
+      <c r="E30" s="10" t="n">
         <v>50.338</v>
       </c>
-      <c r="F30" s="17" t="n">
+      <c r="F30" s="10" t="n">
         <v>638.53</v>
       </c>
-      <c r="G30" s="15" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="H30" s="15" t="inlineStr">
+      <c r="G30" s="1" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H30" s="1" t="inlineStr">
         <is>
           <t>PCS</t>
         </is>
@@ -2450,12 +2441,12 @@
           <t>spodnie</t>
         </is>
       </c>
-      <c r="J30" s="15" t="inlineStr">
-        <is>
-          <t>CN</t>
-        </is>
-      </c>
-      <c r="K30" s="15" t="inlineStr">
+      <c r="J30" s="1" t="inlineStr">
+        <is>
+          <t>CN</t>
+        </is>
+      </c>
+      <c r="K30" s="1" t="inlineStr">
         <is>
           <t>100</t>
         </is>
@@ -2465,32 +2456,32 @@
       <c r="N30" s="5" t="n"/>
     </row>
     <row r="31">
-      <c r="A31" s="15" t="n">
+      <c r="A31" s="1" t="n">
         <v>30</v>
       </c>
-      <c r="B31" s="18" t="inlineStr">
+      <c r="B31" s="9" t="inlineStr">
         <is>
           <t>6204629090</t>
         </is>
       </c>
-      <c r="C31" s="15" t="n">
+      <c r="C31" s="1" t="n">
         <v>1148</v>
       </c>
-      <c r="D31" s="17" t="n">
+      <c r="D31" s="10" t="n">
         <v>166.766</v>
       </c>
-      <c r="E31" s="17" t="n">
+      <c r="E31" s="10" t="n">
         <v>176.066</v>
       </c>
-      <c r="F31" s="17" t="n">
+      <c r="F31" s="10" t="n">
         <v>3249.1</v>
       </c>
-      <c r="G31" s="15" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="H31" s="15" t="inlineStr">
+      <c r="G31" s="1" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H31" s="1" t="inlineStr">
         <is>
           <t>PCS</t>
         </is>
@@ -2500,12 +2491,12 @@
           <t>spodenki</t>
         </is>
       </c>
-      <c r="J31" s="15" t="inlineStr">
-        <is>
-          <t>CN</t>
-        </is>
-      </c>
-      <c r="K31" s="15" t="inlineStr">
+      <c r="J31" s="1" t="inlineStr">
+        <is>
+          <t>CN</t>
+        </is>
+      </c>
+      <c r="K31" s="1" t="inlineStr">
         <is>
           <t>100</t>
         </is>
@@ -2515,32 +2506,32 @@
       <c r="N31" s="5" t="n"/>
     </row>
     <row r="32">
-      <c r="A32" s="15" t="n">
+      <c r="A32" s="1" t="n">
         <v>31</v>
       </c>
-      <c r="B32" s="18" t="inlineStr">
+      <c r="B32" s="9" t="inlineStr">
         <is>
           <t>6204625990</t>
         </is>
       </c>
-      <c r="C32" s="15" t="n">
+      <c r="C32" s="1" t="n">
         <v>27</v>
       </c>
-      <c r="D32" s="17" t="n">
+      <c r="D32" s="10" t="n">
         <v>12.34</v>
       </c>
-      <c r="E32" s="17" t="n">
+      <c r="E32" s="10" t="n">
         <v>12.766</v>
       </c>
-      <c r="F32" s="17" t="n">
+      <c r="F32" s="10" t="n">
         <v>154.71</v>
       </c>
-      <c r="G32" s="15" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="H32" s="15" t="inlineStr">
+      <c r="G32" s="1" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H32" s="1" t="inlineStr">
         <is>
           <t>PCS</t>
         </is>
@@ -2550,12 +2541,12 @@
           <t>ogrodniczki</t>
         </is>
       </c>
-      <c r="J32" s="15" t="inlineStr">
-        <is>
-          <t>CN</t>
-        </is>
-      </c>
-      <c r="K32" s="15" t="inlineStr">
+      <c r="J32" s="1" t="inlineStr">
+        <is>
+          <t>CN</t>
+        </is>
+      </c>
+      <c r="K32" s="1" t="inlineStr">
         <is>
           <t>100</t>
         </is>
@@ -2565,32 +2556,32 @@
       <c r="N32" s="5" t="n"/>
     </row>
     <row r="33">
-      <c r="A33" s="15" t="n">
+      <c r="A33" s="1" t="n">
         <v>32</v>
       </c>
-      <c r="B33" s="18" t="inlineStr">
+      <c r="B33" s="9" t="inlineStr">
         <is>
           <t>6204430000</t>
         </is>
       </c>
-      <c r="C33" s="15" t="n">
+      <c r="C33" s="1" t="n">
         <v>2265</v>
       </c>
-      <c r="D33" s="17" t="n">
+      <c r="D33" s="10" t="n">
         <v>629.351</v>
       </c>
-      <c r="E33" s="17" t="n">
+      <c r="E33" s="10" t="n">
         <v>661.061</v>
       </c>
-      <c r="F33" s="17" t="n">
+      <c r="F33" s="10" t="n">
         <v>9404.57</v>
       </c>
-      <c r="G33" s="15" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="H33" s="15" t="inlineStr">
+      <c r="G33" s="1" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H33" s="1" t="inlineStr">
         <is>
           <t>PCS</t>
         </is>
@@ -2600,12 +2591,12 @@
           <t>sukienka</t>
         </is>
       </c>
-      <c r="J33" s="15" t="inlineStr">
-        <is>
-          <t>CN</t>
-        </is>
-      </c>
-      <c r="K33" s="15" t="inlineStr">
+      <c r="J33" s="1" t="inlineStr">
+        <is>
+          <t>CN</t>
+        </is>
+      </c>
+      <c r="K33" s="1" t="inlineStr">
         <is>
           <t>100</t>
         </is>
@@ -2615,32 +2606,32 @@
       <c r="N33" s="5" t="n"/>
     </row>
     <row r="34">
-      <c r="A34" s="15" t="n">
+      <c r="A34" s="1" t="n">
         <v>33</v>
       </c>
-      <c r="B34" s="18" t="inlineStr">
+      <c r="B34" s="9" t="inlineStr">
         <is>
           <t>6204530090</t>
         </is>
       </c>
-      <c r="C34" s="15" t="n">
+      <c r="C34" s="1" t="n">
         <v>25</v>
       </c>
-      <c r="D34" s="17" t="n">
+      <c r="D34" s="10" t="n">
         <v>4.224</v>
       </c>
-      <c r="E34" s="17" t="n">
+      <c r="E34" s="10" t="n">
         <v>4.354</v>
       </c>
-      <c r="F34" s="17" t="n">
+      <c r="F34" s="10" t="n">
         <v>72.05</v>
       </c>
-      <c r="G34" s="15" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="H34" s="15" t="inlineStr">
+      <c r="G34" s="1" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H34" s="1" t="inlineStr">
         <is>
           <t>PCS</t>
         </is>
@@ -2650,12 +2641,12 @@
           <t>spódnica</t>
         </is>
       </c>
-      <c r="J34" s="15" t="inlineStr">
-        <is>
-          <t>CN</t>
-        </is>
-      </c>
-      <c r="K34" s="15" t="inlineStr">
+      <c r="J34" s="1" t="inlineStr">
+        <is>
+          <t>CN</t>
+        </is>
+      </c>
+      <c r="K34" s="1" t="inlineStr">
         <is>
           <t>100</t>
         </is>
@@ -2665,32 +2656,32 @@
       <c r="N34" s="5" t="n"/>
     </row>
     <row r="35">
-      <c r="A35" s="15" t="n">
+      <c r="A35" s="1" t="n">
         <v>34</v>
       </c>
-      <c r="B35" s="18" t="inlineStr">
+      <c r="B35" s="9" t="inlineStr">
         <is>
           <t>3926200000</t>
         </is>
       </c>
-      <c r="C35" s="15" t="n">
+      <c r="C35" s="1" t="n">
         <v>13</v>
       </c>
-      <c r="D35" s="17" t="n">
+      <c r="D35" s="10" t="n">
         <v>0.949</v>
       </c>
-      <c r="E35" s="17" t="n">
+      <c r="E35" s="10" t="n">
         <v>0.988</v>
       </c>
-      <c r="F35" s="17" t="n">
+      <c r="F35" s="10" t="n">
         <v>17.94</v>
       </c>
-      <c r="G35" s="15" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="H35" s="15" t="inlineStr">
+      <c r="G35" s="1" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H35" s="1" t="inlineStr">
         <is>
           <t>PCS</t>
         </is>
@@ -2700,12 +2691,12 @@
           <t>pasek</t>
         </is>
       </c>
-      <c r="J35" s="15" t="inlineStr">
-        <is>
-          <t>CN</t>
-        </is>
-      </c>
-      <c r="K35" s="15" t="inlineStr">
+      <c r="J35" s="1" t="inlineStr">
+        <is>
+          <t>CN</t>
+        </is>
+      </c>
+      <c r="K35" s="1" t="inlineStr">
         <is>
           <t>100</t>
         </is>
@@ -2715,32 +2706,32 @@
       <c r="N35" s="5" t="n"/>
     </row>
     <row r="36">
-      <c r="A36" s="15" t="n">
+      <c r="A36" s="1" t="n">
         <v>35</v>
       </c>
-      <c r="B36" s="18" t="inlineStr">
+      <c r="B36" s="9" t="inlineStr">
         <is>
           <t>6104220000</t>
         </is>
       </c>
-      <c r="C36" s="15" t="n">
+      <c r="C36" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="D36" s="17" t="n">
+      <c r="D36" s="10" t="n">
         <v>2.316</v>
       </c>
-      <c r="E36" s="17" t="n">
+      <c r="E36" s="10" t="n">
         <v>2.388</v>
       </c>
-      <c r="F36" s="17" t="n">
+      <c r="F36" s="10" t="n">
         <v>29.58</v>
       </c>
-      <c r="G36" s="15" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="H36" s="15" t="inlineStr">
+      <c r="G36" s="1" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H36" s="1" t="inlineStr">
         <is>
           <t>PCS</t>
         </is>
@@ -2750,12 +2741,12 @@
           <t>komplet</t>
         </is>
       </c>
-      <c r="J36" s="15" t="inlineStr">
-        <is>
-          <t>CN</t>
-        </is>
-      </c>
-      <c r="K36" s="15" t="inlineStr">
+      <c r="J36" s="1" t="inlineStr">
+        <is>
+          <t>CN</t>
+        </is>
+      </c>
+      <c r="K36" s="1" t="inlineStr">
         <is>
           <t>100</t>
         </is>
@@ -2765,32 +2756,32 @@
       <c r="N36" s="5" t="n"/>
     </row>
     <row r="37">
-      <c r="A37" s="15" t="n">
+      <c r="A37" s="1" t="n">
         <v>36</v>
       </c>
-      <c r="B37" s="18" t="inlineStr">
+      <c r="B37" s="9" t="inlineStr">
         <is>
           <t>6103430000</t>
         </is>
       </c>
-      <c r="C37" s="15" t="n">
+      <c r="C37" s="1" t="n">
         <v>21</v>
       </c>
-      <c r="D37" s="17" t="n">
+      <c r="D37" s="10" t="n">
         <v>2.374</v>
       </c>
-      <c r="E37" s="17" t="n">
+      <c r="E37" s="10" t="n">
         <v>2.512</v>
       </c>
-      <c r="F37" s="17" t="n">
+      <c r="F37" s="10" t="n">
         <v>44.1</v>
       </c>
-      <c r="G37" s="15" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="H37" s="15" t="inlineStr">
+      <c r="G37" s="1" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H37" s="1" t="inlineStr">
         <is>
           <t>PCS</t>
         </is>
@@ -2800,12 +2791,12 @@
           <t>spodenki</t>
         </is>
       </c>
-      <c r="J37" s="15" t="inlineStr">
-        <is>
-          <t>CN</t>
-        </is>
-      </c>
-      <c r="K37" s="15" t="inlineStr">
+      <c r="J37" s="1" t="inlineStr">
+        <is>
+          <t>CN</t>
+        </is>
+      </c>
+      <c r="K37" s="1" t="inlineStr">
         <is>
           <t>100</t>
         </is>
@@ -2815,32 +2806,32 @@
       <c r="N37" s="5" t="n"/>
     </row>
     <row r="38">
-      <c r="A38" s="15" t="n">
+      <c r="A38" s="1" t="n">
         <v>37</v>
       </c>
-      <c r="B38" s="18" t="inlineStr">
+      <c r="B38" s="9" t="inlineStr">
         <is>
           <t>6105201000</t>
         </is>
       </c>
-      <c r="C38" s="15" t="n">
+      <c r="C38" s="1" t="n">
         <v>15</v>
       </c>
-      <c r="D38" s="17" t="n">
+      <c r="D38" s="10" t="n">
         <v>1.01</v>
       </c>
-      <c r="E38" s="17" t="n">
+      <c r="E38" s="10" t="n">
         <v>1.1</v>
       </c>
-      <c r="F38" s="17" t="n">
+      <c r="F38" s="10" t="n">
         <v>19.2</v>
       </c>
-      <c r="G38" s="15" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="H38" s="15" t="inlineStr">
+      <c r="G38" s="1" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H38" s="1" t="inlineStr">
         <is>
           <t>PCS</t>
         </is>
@@ -2850,12 +2841,12 @@
           <t>koszula</t>
         </is>
       </c>
-      <c r="J38" s="15" t="inlineStr">
-        <is>
-          <t>CN</t>
-        </is>
-      </c>
-      <c r="K38" s="15" t="inlineStr">
+      <c r="J38" s="1" t="inlineStr">
+        <is>
+          <t>CN</t>
+        </is>
+      </c>
+      <c r="K38" s="1" t="inlineStr">
         <is>
           <t>100</t>
         </is>
@@ -2865,32 +2856,32 @@
       <c r="N38" s="5" t="n"/>
     </row>
     <row r="39">
-      <c r="A39" s="15" t="n">
+      <c r="A39" s="1" t="n">
         <v>38</v>
       </c>
-      <c r="B39" s="18" t="inlineStr">
+      <c r="B39" s="9" t="inlineStr">
         <is>
           <t>6103230000</t>
         </is>
       </c>
-      <c r="C39" s="15" t="n">
+      <c r="C39" s="1" t="n">
         <v>172</v>
       </c>
-      <c r="D39" s="17" t="n">
+      <c r="D39" s="10" t="n">
         <v>49.06</v>
       </c>
-      <c r="E39" s="17" t="n">
+      <c r="E39" s="10" t="n">
         <v>51.399</v>
       </c>
-      <c r="F39" s="17" t="n">
+      <c r="F39" s="10" t="n">
         <v>557.45</v>
       </c>
-      <c r="G39" s="15" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="H39" s="15" t="inlineStr">
+      <c r="G39" s="1" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H39" s="1" t="inlineStr">
         <is>
           <t>PCS</t>
         </is>
@@ -2900,12 +2891,12 @@
           <t>komplet</t>
         </is>
       </c>
-      <c r="J39" s="15" t="inlineStr">
-        <is>
-          <t>CN</t>
-        </is>
-      </c>
-      <c r="K39" s="15" t="inlineStr">
+      <c r="J39" s="1" t="inlineStr">
+        <is>
+          <t>CN</t>
+        </is>
+      </c>
+      <c r="K39" s="1" t="inlineStr">
         <is>
           <t>100</t>
         </is>
@@ -2915,32 +2906,32 @@
       <c r="N39" s="5" t="n"/>
     </row>
     <row r="40">
-      <c r="A40" s="15" t="n">
+      <c r="A40" s="1" t="n">
         <v>39</v>
       </c>
-      <c r="B40" s="18" t="inlineStr">
+      <c r="B40" s="9" t="inlineStr">
         <is>
           <t>3926909790</t>
         </is>
       </c>
-      <c r="C40" s="15" t="n">
+      <c r="C40" s="1" t="n">
         <v>121</v>
       </c>
-      <c r="D40" s="17" t="n">
+      <c r="D40" s="10" t="n">
         <v>7.343</v>
       </c>
-      <c r="E40" s="17" t="n">
+      <c r="E40" s="10" t="n">
         <v>8.589</v>
       </c>
-      <c r="F40" s="17" t="n">
+      <c r="F40" s="10" t="n">
         <v>152.2</v>
       </c>
-      <c r="G40" s="15" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="H40" s="15" t="inlineStr">
+      <c r="G40" s="1" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H40" s="1" t="inlineStr">
         <is>
           <t>PCS</t>
         </is>
@@ -2950,12 +2941,12 @@
           <t>zawieszka do bagażu</t>
         </is>
       </c>
-      <c r="J40" s="15" t="inlineStr">
-        <is>
-          <t>CN</t>
-        </is>
-      </c>
-      <c r="K40" s="15" t="inlineStr">
+      <c r="J40" s="1" t="inlineStr">
+        <is>
+          <t>CN</t>
+        </is>
+      </c>
+      <c r="K40" s="1" t="inlineStr">
         <is>
           <t>100</t>
         </is>
@@ -2965,32 +2956,32 @@
       <c r="N40" s="5" t="n"/>
     </row>
     <row r="41">
-      <c r="A41" s="15" t="n">
+      <c r="A41" s="1" t="n">
         <v>40</v>
       </c>
-      <c r="B41" s="18" t="inlineStr">
+      <c r="B41" s="9" t="inlineStr">
         <is>
           <t>6204228090</t>
         </is>
       </c>
-      <c r="C41" s="15" t="n">
+      <c r="C41" s="1" t="n">
         <v>37</v>
       </c>
-      <c r="D41" s="17" t="n">
+      <c r="D41" s="10" t="n">
         <v>10.112</v>
       </c>
-      <c r="E41" s="17" t="n">
+      <c r="E41" s="10" t="n">
         <v>10.546</v>
       </c>
-      <c r="F41" s="17" t="n">
+      <c r="F41" s="10" t="n">
         <v>168.26</v>
       </c>
-      <c r="G41" s="15" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="H41" s="15" t="inlineStr">
+      <c r="G41" s="1" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H41" s="1" t="inlineStr">
         <is>
           <t>PCS</t>
         </is>
@@ -3000,12 +2991,12 @@
           <t>komplet</t>
         </is>
       </c>
-      <c r="J41" s="15" t="inlineStr">
-        <is>
-          <t>CN</t>
-        </is>
-      </c>
-      <c r="K41" s="15" t="inlineStr">
+      <c r="J41" s="1" t="inlineStr">
+        <is>
+          <t>CN</t>
+        </is>
+      </c>
+      <c r="K41" s="1" t="inlineStr">
         <is>
           <t>100</t>
         </is>
@@ -3015,32 +3006,32 @@
       <c r="N41" s="5" t="n"/>
     </row>
     <row r="42">
-      <c r="A42" s="15" t="n">
+      <c r="A42" s="1" t="n">
         <v>41</v>
       </c>
-      <c r="B42" s="18" t="inlineStr">
+      <c r="B42" s="9" t="inlineStr">
         <is>
           <t>6212900000</t>
         </is>
       </c>
-      <c r="C42" s="15" t="n">
+      <c r="C42" s="1" t="n">
         <v>202</v>
       </c>
-      <c r="D42" s="17" t="n">
+      <c r="D42" s="10" t="n">
         <v>4.346</v>
       </c>
-      <c r="E42" s="17" t="n">
+      <c r="E42" s="10" t="n">
         <v>6.132</v>
       </c>
-      <c r="F42" s="17" t="n">
+      <c r="F42" s="10" t="n">
         <v>217.28</v>
       </c>
-      <c r="G42" s="15" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="H42" s="15" t="inlineStr">
+      <c r="G42" s="1" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H42" s="1" t="inlineStr">
         <is>
           <t>PCS</t>
         </is>
@@ -3050,12 +3041,12 @@
           <t>przedłużka do biustonosza</t>
         </is>
       </c>
-      <c r="J42" s="15" t="inlineStr">
-        <is>
-          <t>CN</t>
-        </is>
-      </c>
-      <c r="K42" s="15" t="inlineStr">
+      <c r="J42" s="1" t="inlineStr">
+        <is>
+          <t>CN</t>
+        </is>
+      </c>
+      <c r="K42" s="1" t="inlineStr">
         <is>
           <t>100</t>
         </is>
@@ -3065,32 +3056,32 @@
       <c r="N42" s="5" t="n"/>
     </row>
     <row r="43">
-      <c r="A43" s="15" t="n">
+      <c r="A43" s="1" t="n">
         <v>42</v>
       </c>
-      <c r="B43" s="18" t="inlineStr">
+      <c r="B43" s="9" t="inlineStr">
         <is>
           <t>6117100000</t>
         </is>
       </c>
-      <c r="C43" s="15" t="n">
+      <c r="C43" s="1" t="n">
         <v>22</v>
       </c>
-      <c r="D43" s="17" t="n">
+      <c r="D43" s="10" t="n">
         <v>1.011</v>
       </c>
-      <c r="E43" s="17" t="n">
+      <c r="E43" s="10" t="n">
         <v>1.166</v>
       </c>
-      <c r="F43" s="17" t="n">
+      <c r="F43" s="10" t="n">
         <v>33.13</v>
       </c>
-      <c r="G43" s="15" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="H43" s="15" t="inlineStr">
+      <c r="G43" s="1" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H43" s="1" t="inlineStr">
         <is>
           <t>PCS</t>
         </is>
@@ -3100,12 +3091,12 @@
           <t>szalik</t>
         </is>
       </c>
-      <c r="J43" s="15" t="inlineStr">
-        <is>
-          <t>CN</t>
-        </is>
-      </c>
-      <c r="K43" s="15" t="inlineStr">
+      <c r="J43" s="1" t="inlineStr">
+        <is>
+          <t>CN</t>
+        </is>
+      </c>
+      <c r="K43" s="1" t="inlineStr">
         <is>
           <t>100</t>
         </is>
@@ -3115,32 +3106,32 @@
       <c r="N43" s="5" t="n"/>
     </row>
     <row r="44">
-      <c r="A44" s="15" t="n">
+      <c r="A44" s="1" t="n">
         <v>43</v>
       </c>
-      <c r="B44" s="18" t="inlineStr">
+      <c r="B44" s="9" t="inlineStr">
         <is>
           <t>6107990020</t>
         </is>
       </c>
-      <c r="C44" s="15" t="n">
+      <c r="C44" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="D44" s="17" t="n">
+      <c r="D44" s="10" t="n">
         <v>1.57</v>
       </c>
-      <c r="E44" s="17" t="n">
+      <c r="E44" s="10" t="n">
         <v>1.62</v>
       </c>
-      <c r="F44" s="17" t="n">
+      <c r="F44" s="10" t="n">
         <v>15.25</v>
       </c>
-      <c r="G44" s="15" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="H44" s="15" t="inlineStr">
+      <c r="G44" s="1" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H44" s="1" t="inlineStr">
         <is>
           <t>PCS</t>
         </is>
@@ -3150,12 +3141,12 @@
           <t>spodnie od piżamy</t>
         </is>
       </c>
-      <c r="J44" s="15" t="inlineStr">
-        <is>
-          <t>CN</t>
-        </is>
-      </c>
-      <c r="K44" s="15" t="inlineStr">
+      <c r="J44" s="1" t="inlineStr">
+        <is>
+          <t>CN</t>
+        </is>
+      </c>
+      <c r="K44" s="1" t="inlineStr">
         <is>
           <t>100</t>
         </is>
@@ -3165,32 +3156,32 @@
       <c r="N44" s="5" t="n"/>
     </row>
     <row r="45">
-      <c r="A45" s="15" t="n">
+      <c r="A45" s="1" t="n">
         <v>44</v>
       </c>
-      <c r="B45" s="18" t="inlineStr">
+      <c r="B45" s="9" t="inlineStr">
         <is>
           <t>6103220000</t>
         </is>
       </c>
-      <c r="C45" s="15" t="n">
+      <c r="C45" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="D45" s="17" t="n">
+      <c r="D45" s="10" t="n">
         <v>5.44</v>
       </c>
-      <c r="E45" s="17" t="n">
+      <c r="E45" s="10" t="n">
         <v>5.6</v>
       </c>
-      <c r="F45" s="17" t="n">
+      <c r="F45" s="10" t="n">
         <v>63</v>
       </c>
-      <c r="G45" s="15" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="H45" s="15" t="inlineStr">
+      <c r="G45" s="1" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H45" s="1" t="inlineStr">
         <is>
           <t>PCS</t>
         </is>
@@ -3200,12 +3191,12 @@
           <t>komplet</t>
         </is>
       </c>
-      <c r="J45" s="15" t="inlineStr">
-        <is>
-          <t>CN</t>
-        </is>
-      </c>
-      <c r="K45" s="15" t="inlineStr">
+      <c r="J45" s="1" t="inlineStr">
+        <is>
+          <t>CN</t>
+        </is>
+      </c>
+      <c r="K45" s="1" t="inlineStr">
         <is>
           <t>100</t>
         </is>
@@ -3215,32 +3206,32 @@
       <c r="N45" s="5" t="n"/>
     </row>
     <row r="46">
-      <c r="A46" s="15" t="n">
+      <c r="A46" s="1" t="n">
         <v>45</v>
       </c>
-      <c r="B46" s="18" t="inlineStr">
+      <c r="B46" s="9" t="inlineStr">
         <is>
           <t>6205200090</t>
         </is>
       </c>
-      <c r="C46" s="15" t="n">
+      <c r="C46" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="D46" s="17" t="n">
+      <c r="D46" s="10" t="n">
         <v>0.104</v>
       </c>
-      <c r="E46" s="17" t="n">
+      <c r="E46" s="10" t="n">
         <v>0.11</v>
       </c>
-      <c r="F46" s="17" t="n">
+      <c r="F46" s="10" t="n">
         <v>3.42</v>
       </c>
-      <c r="G46" s="15" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="H46" s="15" t="inlineStr">
+      <c r="G46" s="1" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H46" s="1" t="inlineStr">
         <is>
           <t>PCS</t>
         </is>
@@ -3250,12 +3241,12 @@
           <t>koszula</t>
         </is>
       </c>
-      <c r="J46" s="15" t="inlineStr">
-        <is>
-          <t>CN</t>
-        </is>
-      </c>
-      <c r="K46" s="15" t="inlineStr">
+      <c r="J46" s="1" t="inlineStr">
+        <is>
+          <t>CN</t>
+        </is>
+      </c>
+      <c r="K46" s="1" t="inlineStr">
         <is>
           <t>100</t>
         </is>
@@ -3265,32 +3256,32 @@
       <c r="N46" s="5" t="n"/>
     </row>
     <row r="47">
-      <c r="A47" s="15" t="n">
+      <c r="A47" s="1" t="n">
         <v>46</v>
       </c>
-      <c r="B47" s="18" t="inlineStr">
+      <c r="B47" s="9" t="inlineStr">
         <is>
           <t>9620001000</t>
         </is>
       </c>
-      <c r="C47" s="15" t="n">
+      <c r="C47" s="1" t="n">
         <v>77</v>
       </c>
-      <c r="D47" s="17" t="n">
+      <c r="D47" s="10" t="n">
         <v>9.279999999999999</v>
       </c>
-      <c r="E47" s="17" t="n">
+      <c r="E47" s="10" t="n">
         <v>10.52</v>
       </c>
-      <c r="F47" s="17" t="n">
+      <c r="F47" s="10" t="n">
         <v>129.49</v>
       </c>
-      <c r="G47" s="15" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="H47" s="15" t="inlineStr">
+      <c r="G47" s="1" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H47" s="1" t="inlineStr">
         <is>
           <t>PCS</t>
         </is>
@@ -3300,12 +3291,12 @@
           <t>uchwyt do monitora</t>
         </is>
       </c>
-      <c r="J47" s="15" t="inlineStr">
-        <is>
-          <t>CN</t>
-        </is>
-      </c>
-      <c r="K47" s="15" t="inlineStr">
+      <c r="J47" s="1" t="inlineStr">
+        <is>
+          <t>CN</t>
+        </is>
+      </c>
+      <c r="K47" s="1" t="inlineStr">
         <is>
           <t>100</t>
         </is>
@@ -3315,32 +3306,32 @@
       <c r="N47" s="5" t="n"/>
     </row>
     <row r="48">
-      <c r="A48" s="15" t="n">
+      <c r="A48" s="1" t="n">
         <v>47</v>
       </c>
-      <c r="B48" s="18" t="inlineStr">
+      <c r="B48" s="9" t="inlineStr">
         <is>
           <t>6204639090</t>
         </is>
       </c>
-      <c r="C48" s="15" t="n">
+      <c r="C48" s="1" t="n">
         <v>25</v>
       </c>
-      <c r="D48" s="17" t="n">
+      <c r="D48" s="10" t="n">
         <v>1.581</v>
       </c>
-      <c r="E48" s="17" t="n">
+      <c r="E48" s="10" t="n">
         <v>1.703</v>
       </c>
-      <c r="F48" s="17" t="n">
+      <c r="F48" s="10" t="n">
         <v>43.62</v>
       </c>
-      <c r="G48" s="15" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="H48" s="15" t="inlineStr">
+      <c r="G48" s="1" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H48" s="1" t="inlineStr">
         <is>
           <t>PCS</t>
         </is>
@@ -3350,12 +3341,12 @@
           <t>spodenki</t>
         </is>
       </c>
-      <c r="J48" s="15" t="inlineStr">
-        <is>
-          <t>CN</t>
-        </is>
-      </c>
-      <c r="K48" s="15" t="inlineStr">
+      <c r="J48" s="1" t="inlineStr">
+        <is>
+          <t>CN</t>
+        </is>
+      </c>
+      <c r="K48" s="1" t="inlineStr">
         <is>
           <t>100</t>
         </is>
@@ -3365,32 +3356,32 @@
       <c r="N48" s="5" t="n"/>
     </row>
     <row r="49">
-      <c r="A49" s="15" t="n">
+      <c r="A49" s="1" t="n">
         <v>48</v>
       </c>
-      <c r="B49" s="18" t="inlineStr">
+      <c r="B49" s="9" t="inlineStr">
         <is>
           <t>9615900000</t>
         </is>
       </c>
-      <c r="C49" s="15" t="n">
+      <c r="C49" s="1" t="n">
         <v>213</v>
       </c>
-      <c r="D49" s="17" t="n">
+      <c r="D49" s="10" t="n">
         <v>16.952</v>
       </c>
-      <c r="E49" s="17" t="n">
+      <c r="E49" s="10" t="n">
         <v>18.2</v>
       </c>
-      <c r="F49" s="17" t="n">
+      <c r="F49" s="10" t="n">
         <v>332.79</v>
       </c>
-      <c r="G49" s="15" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="H49" s="15" t="inlineStr">
+      <c r="G49" s="1" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H49" s="1" t="inlineStr">
         <is>
           <t>PCS</t>
         </is>
@@ -3400,12 +3391,12 @@
           <t>zestaw wałków do włosów</t>
         </is>
       </c>
-      <c r="J49" s="15" t="inlineStr">
-        <is>
-          <t>CN</t>
-        </is>
-      </c>
-      <c r="K49" s="15" t="inlineStr">
+      <c r="J49" s="1" t="inlineStr">
+        <is>
+          <t>CN</t>
+        </is>
+      </c>
+      <c r="K49" s="1" t="inlineStr">
         <is>
           <t>100</t>
         </is>
@@ -3415,32 +3406,32 @@
       <c r="N49" s="5" t="n"/>
     </row>
     <row r="50">
-      <c r="A50" s="15" t="n">
+      <c r="A50" s="1" t="n">
         <v>49</v>
       </c>
-      <c r="B50" s="18" t="inlineStr">
+      <c r="B50" s="9" t="inlineStr">
         <is>
           <t>6111209000</t>
         </is>
       </c>
-      <c r="C50" s="15" t="n">
+      <c r="C50" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="D50" s="17" t="n">
+      <c r="D50" s="10" t="n">
         <v>2.072</v>
       </c>
-      <c r="E50" s="17" t="n">
+      <c r="E50" s="10" t="n">
         <v>2.136</v>
       </c>
-      <c r="F50" s="17" t="n">
+      <c r="F50" s="10" t="n">
         <v>58.16</v>
       </c>
-      <c r="G50" s="15" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="H50" s="15" t="inlineStr">
+      <c r="G50" s="1" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H50" s="1" t="inlineStr">
         <is>
           <t>PCS</t>
         </is>
@@ -3450,12 +3441,12 @@
           <t>komplet</t>
         </is>
       </c>
-      <c r="J50" s="15" t="inlineStr">
-        <is>
-          <t>CN</t>
-        </is>
-      </c>
-      <c r="K50" s="15" t="inlineStr">
+      <c r="J50" s="1" t="inlineStr">
+        <is>
+          <t>CN</t>
+        </is>
+      </c>
+      <c r="K50" s="1" t="inlineStr">
         <is>
           <t>100</t>
         </is>
@@ -3465,32 +3456,32 @@
       <c r="N50" s="5" t="n"/>
     </row>
     <row r="51">
-      <c r="A51" s="15" t="n">
+      <c r="A51" s="1" t="n">
         <v>50</v>
       </c>
-      <c r="B51" s="18" t="inlineStr">
+      <c r="B51" s="9" t="inlineStr">
         <is>
           <t>6109100090</t>
         </is>
       </c>
-      <c r="C51" s="15" t="n">
+      <c r="C51" s="1" t="n">
         <v>14</v>
       </c>
-      <c r="D51" s="17" t="n">
+      <c r="D51" s="10" t="n">
         <v>0.756</v>
       </c>
-      <c r="E51" s="17" t="n">
+      <c r="E51" s="10" t="n">
         <v>0.8120000000000001</v>
       </c>
-      <c r="F51" s="17" t="n">
+      <c r="F51" s="10" t="n">
         <v>15.96</v>
       </c>
-      <c r="G51" s="15" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="H51" s="15" t="inlineStr">
+      <c r="G51" s="1" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H51" s="1" t="inlineStr">
         <is>
           <t>PCS</t>
         </is>
@@ -3500,12 +3491,12 @@
           <t>topy damskie</t>
         </is>
       </c>
-      <c r="J51" s="15" t="inlineStr">
-        <is>
-          <t>CN</t>
-        </is>
-      </c>
-      <c r="K51" s="15" t="inlineStr">
+      <c r="J51" s="1" t="inlineStr">
+        <is>
+          <t>CN</t>
+        </is>
+      </c>
+      <c r="K51" s="1" t="inlineStr">
         <is>
           <t>100</t>
         </is>
@@ -3515,32 +3506,32 @@
       <c r="N51" s="5" t="n"/>
     </row>
     <row r="52">
-      <c r="A52" s="15" t="n">
+      <c r="A52" s="1" t="n">
         <v>51</v>
       </c>
-      <c r="B52" s="18" t="inlineStr">
+      <c r="B52" s="9" t="inlineStr">
         <is>
           <t>9603309000</t>
         </is>
       </c>
-      <c r="C52" s="15" t="n">
+      <c r="C52" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="D52" s="17" t="n">
+      <c r="D52" s="10" t="n">
         <v>0.765</v>
       </c>
-      <c r="E52" s="17" t="n">
+      <c r="E52" s="10" t="n">
         <v>0.819</v>
       </c>
-      <c r="F52" s="17" t="n">
+      <c r="F52" s="10" t="n">
         <v>14.58</v>
       </c>
-      <c r="G52" s="15" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="H52" s="15" t="inlineStr">
+      <c r="G52" s="1" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H52" s="1" t="inlineStr">
         <is>
           <t>PCS</t>
         </is>
@@ -3550,12 +3541,12 @@
           <t>zestaw pędzli do makijażu</t>
         </is>
       </c>
-      <c r="J52" s="15" t="inlineStr">
-        <is>
-          <t>CN</t>
-        </is>
-      </c>
-      <c r="K52" s="15" t="inlineStr">
+      <c r="J52" s="1" t="inlineStr">
+        <is>
+          <t>CN</t>
+        </is>
+      </c>
+      <c r="K52" s="1" t="inlineStr">
         <is>
           <t>100</t>
         </is>
@@ -3565,32 +3556,32 @@
       <c r="N52" s="5" t="n"/>
     </row>
     <row r="53">
-      <c r="A53" s="15" t="n">
+      <c r="A53" s="1" t="n">
         <v>52</v>
       </c>
-      <c r="B53" s="18" t="inlineStr">
+      <c r="B53" s="9" t="inlineStr">
         <is>
           <t>6402993900</t>
         </is>
       </c>
-      <c r="C53" s="15" t="n">
+      <c r="C53" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="D53" s="17" t="n">
+      <c r="D53" s="10" t="n">
         <v>1.904</v>
       </c>
-      <c r="E53" s="17" t="n">
+      <c r="E53" s="10" t="n">
         <v>2.128</v>
       </c>
-      <c r="F53" s="17" t="n">
+      <c r="F53" s="10" t="n">
         <v>15.67</v>
       </c>
-      <c r="G53" s="15" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="H53" s="15" t="inlineStr">
+      <c r="G53" s="1" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H53" s="1" t="inlineStr">
         <is>
           <t>PCS</t>
         </is>
@@ -3600,12 +3591,12 @@
           <t>kapcie</t>
         </is>
       </c>
-      <c r="J53" s="15" t="inlineStr">
-        <is>
-          <t>CN</t>
-        </is>
-      </c>
-      <c r="K53" s="15" t="inlineStr">
+      <c r="J53" s="1" t="inlineStr">
+        <is>
+          <t>CN</t>
+        </is>
+      </c>
+      <c r="K53" s="1" t="inlineStr">
         <is>
           <t>100</t>
         </is>
@@ -3615,32 +3606,32 @@
       <c r="N53" s="5" t="n"/>
     </row>
     <row r="54">
-      <c r="A54" s="15" t="n">
+      <c r="A54" s="1" t="n">
         <v>53</v>
       </c>
-      <c r="B54" s="18" t="inlineStr">
+      <c r="B54" s="9" t="inlineStr">
         <is>
           <t>9403700000</t>
         </is>
       </c>
-      <c r="C54" s="15" t="n">
+      <c r="C54" s="1" t="n">
         <v>34</v>
       </c>
-      <c r="D54" s="17" t="n">
+      <c r="D54" s="10" t="n">
         <v>7.998</v>
       </c>
-      <c r="E54" s="17" t="n">
+      <c r="E54" s="10" t="n">
         <v>8.279999999999999</v>
       </c>
-      <c r="F54" s="17" t="n">
+      <c r="F54" s="10" t="n">
         <v>81.81999999999999</v>
       </c>
-      <c r="G54" s="15" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="H54" s="15" t="inlineStr">
+      <c r="G54" s="1" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H54" s="1" t="inlineStr">
         <is>
           <t>PCS</t>
         </is>
@@ -3650,12 +3641,12 @@
           <t>półka ścienna</t>
         </is>
       </c>
-      <c r="J54" s="15" t="inlineStr">
-        <is>
-          <t>CN</t>
-        </is>
-      </c>
-      <c r="K54" s="15" t="inlineStr">
+      <c r="J54" s="1" t="inlineStr">
+        <is>
+          <t>CN</t>
+        </is>
+      </c>
+      <c r="K54" s="1" t="inlineStr">
         <is>
           <t>100</t>
         </is>
@@ -3665,32 +3656,32 @@
       <c r="N54" s="5" t="n"/>
     </row>
     <row r="55">
-      <c r="A55" s="15" t="n">
+      <c r="A55" s="1" t="n">
         <v>54</v>
       </c>
-      <c r="B55" s="18" t="inlineStr">
+      <c r="B55" s="9" t="inlineStr">
         <is>
           <t>3925901000</t>
         </is>
       </c>
-      <c r="C55" s="15" t="n">
+      <c r="C55" s="1" t="n">
         <v>103</v>
       </c>
-      <c r="D55" s="17" t="n">
+      <c r="D55" s="10" t="n">
         <v>17.721</v>
       </c>
-      <c r="E55" s="17" t="n">
+      <c r="E55" s="10" t="n">
         <v>18.591</v>
       </c>
-      <c r="F55" s="17" t="n">
+      <c r="F55" s="10" t="n">
         <v>194.07</v>
       </c>
-      <c r="G55" s="15" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="H55" s="15" t="inlineStr">
+      <c r="G55" s="1" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H55" s="1" t="inlineStr">
         <is>
           <t>PCS</t>
         </is>
@@ -3700,12 +3691,12 @@
           <t>hak ścienny</t>
         </is>
       </c>
-      <c r="J55" s="15" t="inlineStr">
-        <is>
-          <t>CN</t>
-        </is>
-      </c>
-      <c r="K55" s="15" t="inlineStr">
+      <c r="J55" s="1" t="inlineStr">
+        <is>
+          <t>CN</t>
+        </is>
+      </c>
+      <c r="K55" s="1" t="inlineStr">
         <is>
           <t>100</t>
         </is>
@@ -3715,32 +3706,32 @@
       <c r="N55" s="5" t="n"/>
     </row>
     <row r="56">
-      <c r="A56" s="15" t="n">
+      <c r="A56" s="1" t="n">
         <v>55</v>
       </c>
-      <c r="B56" s="18" t="inlineStr">
+      <c r="B56" s="9" t="inlineStr">
         <is>
           <t>6109100010</t>
         </is>
       </c>
-      <c r="C56" s="15" t="n">
+      <c r="C56" s="1" t="n">
         <v>172</v>
       </c>
-      <c r="D56" s="17" t="n">
+      <c r="D56" s="10" t="n">
         <v>22.914</v>
       </c>
-      <c r="E56" s="17" t="n">
+      <c r="E56" s="10" t="n">
         <v>24.138</v>
       </c>
-      <c r="F56" s="17" t="n">
+      <c r="F56" s="10" t="n">
         <v>567.14</v>
       </c>
-      <c r="G56" s="15" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="H56" s="15" t="inlineStr">
+      <c r="G56" s="1" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H56" s="1" t="inlineStr">
         <is>
           <t>PCS</t>
         </is>
@@ -3750,12 +3741,12 @@
           <t>koszulka</t>
         </is>
       </c>
-      <c r="J56" s="15" t="inlineStr">
-        <is>
-          <t>CN</t>
-        </is>
-      </c>
-      <c r="K56" s="15" t="inlineStr">
+      <c r="J56" s="1" t="inlineStr">
+        <is>
+          <t>CN</t>
+        </is>
+      </c>
+      <c r="K56" s="1" t="inlineStr">
         <is>
           <t>100</t>
         </is>
@@ -3765,32 +3756,32 @@
       <c r="N56" s="5" t="n"/>
     </row>
     <row r="57">
-      <c r="A57" s="15" t="n">
+      <c r="A57" s="1" t="n">
         <v>56</v>
       </c>
-      <c r="B57" s="18" t="inlineStr">
+      <c r="B57" s="9" t="inlineStr">
         <is>
           <t>6114200000</t>
         </is>
       </c>
-      <c r="C57" s="15" t="n">
+      <c r="C57" s="1" t="n">
         <v>18</v>
       </c>
-      <c r="D57" s="17" t="n">
+      <c r="D57" s="10" t="n">
         <v>2.466</v>
       </c>
-      <c r="E57" s="17" t="n">
+      <c r="E57" s="10" t="n">
         <v>2.592</v>
       </c>
-      <c r="F57" s="17" t="n">
+      <c r="F57" s="10" t="n">
         <v>66.23999999999999</v>
       </c>
-      <c r="G57" s="15" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="H57" s="15" t="inlineStr">
+      <c r="G57" s="1" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H57" s="1" t="inlineStr">
         <is>
           <t>PCS</t>
         </is>
@@ -3800,12 +3791,12 @@
           <t>topy damskie</t>
         </is>
       </c>
-      <c r="J57" s="15" t="inlineStr">
-        <is>
-          <t>CN</t>
-        </is>
-      </c>
-      <c r="K57" s="15" t="inlineStr">
+      <c r="J57" s="1" t="inlineStr">
+        <is>
+          <t>CN</t>
+        </is>
+      </c>
+      <c r="K57" s="1" t="inlineStr">
         <is>
           <t>100</t>
         </is>
@@ -3815,32 +3806,32 @@
       <c r="N57" s="5" t="n"/>
     </row>
     <row r="58">
-      <c r="A58" s="15" t="n">
+      <c r="A58" s="1" t="n">
         <v>57</v>
       </c>
-      <c r="B58" s="18" t="inlineStr">
+      <c r="B58" s="9" t="inlineStr">
         <is>
           <t>6204520090</t>
         </is>
       </c>
-      <c r="C58" s="15" t="n">
+      <c r="C58" s="1" t="n">
         <v>174</v>
       </c>
-      <c r="D58" s="17" t="n">
+      <c r="D58" s="10" t="n">
         <v>62.03</v>
       </c>
-      <c r="E58" s="17" t="n">
+      <c r="E58" s="10" t="n">
         <v>64.73</v>
       </c>
-      <c r="F58" s="17" t="n">
+      <c r="F58" s="10" t="n">
         <v>776.8200000000001</v>
       </c>
-      <c r="G58" s="15" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="H58" s="15" t="inlineStr">
+      <c r="G58" s="1" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H58" s="1" t="inlineStr">
         <is>
           <t>PCS</t>
         </is>
@@ -3850,12 +3841,12 @@
           <t>spódnica</t>
         </is>
       </c>
-      <c r="J58" s="15" t="inlineStr">
-        <is>
-          <t>CN</t>
-        </is>
-      </c>
-      <c r="K58" s="15" t="inlineStr">
+      <c r="J58" s="1" t="inlineStr">
+        <is>
+          <t>CN</t>
+        </is>
+      </c>
+      <c r="K58" s="1" t="inlineStr">
         <is>
           <t>100</t>
         </is>
@@ -3865,32 +3856,32 @@
       <c r="N58" s="5" t="n"/>
     </row>
     <row r="59">
-      <c r="A59" s="15" t="n">
+      <c r="A59" s="1" t="n">
         <v>58</v>
       </c>
-      <c r="B59" s="18" t="inlineStr">
+      <c r="B59" s="9" t="inlineStr">
         <is>
           <t>6217100090</t>
         </is>
       </c>
-      <c r="C59" s="15" t="n">
+      <c r="C59" s="1" t="n">
         <v>278</v>
       </c>
-      <c r="D59" s="17" t="n">
+      <c r="D59" s="10" t="n">
         <v>9.632</v>
       </c>
-      <c r="E59" s="17" t="n">
+      <c r="E59" s="10" t="n">
         <v>12.23</v>
       </c>
-      <c r="F59" s="17" t="n">
+      <c r="F59" s="10" t="n">
         <v>353.33</v>
       </c>
-      <c r="G59" s="15" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="H59" s="15" t="inlineStr">
+      <c r="G59" s="1" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H59" s="1" t="inlineStr">
         <is>
           <t>PCS</t>
         </is>
@@ -3900,12 +3891,12 @@
           <t>wkładki laktacyjne</t>
         </is>
       </c>
-      <c r="J59" s="15" t="inlineStr">
-        <is>
-          <t>CN</t>
-        </is>
-      </c>
-      <c r="K59" s="15" t="inlineStr">
+      <c r="J59" s="1" t="inlineStr">
+        <is>
+          <t>CN</t>
+        </is>
+      </c>
+      <c r="K59" s="1" t="inlineStr">
         <is>
           <t>100</t>
         </is>
@@ -3915,32 +3906,32 @@
       <c r="N59" s="5" t="n"/>
     </row>
     <row r="60">
-      <c r="A60" s="15" t="n">
+      <c r="A60" s="1" t="n">
         <v>59</v>
       </c>
-      <c r="B60" s="18" t="inlineStr">
+      <c r="B60" s="9" t="inlineStr">
         <is>
           <t>6107120000</t>
         </is>
       </c>
-      <c r="C60" s="15" t="n">
+      <c r="C60" s="1" t="n">
         <v>23</v>
       </c>
-      <c r="D60" s="17" t="n">
+      <c r="D60" s="10" t="n">
         <v>15.412</v>
       </c>
-      <c r="E60" s="17" t="n">
+      <c r="E60" s="10" t="n">
         <v>16.66</v>
       </c>
-      <c r="F60" s="17" t="n">
+      <c r="F60" s="10" t="n">
         <v>105.77</v>
       </c>
-      <c r="G60" s="15" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="H60" s="15" t="inlineStr">
+      <c r="G60" s="1" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H60" s="1" t="inlineStr">
         <is>
           <t>PCS</t>
         </is>
@@ -3950,12 +3941,12 @@
           <t>bokserki</t>
         </is>
       </c>
-      <c r="J60" s="15" t="inlineStr">
-        <is>
-          <t>CN</t>
-        </is>
-      </c>
-      <c r="K60" s="15" t="inlineStr">
+      <c r="J60" s="1" t="inlineStr">
+        <is>
+          <t>CN</t>
+        </is>
+      </c>
+      <c r="K60" s="1" t="inlineStr">
         <is>
           <t>100</t>
         </is>
@@ -3965,32 +3956,32 @@
       <c r="N60" s="5" t="n"/>
     </row>
     <row r="61">
-      <c r="A61" s="15" t="n">
+      <c r="A61" s="1" t="n">
         <v>60</v>
       </c>
-      <c r="B61" s="18" t="inlineStr">
+      <c r="B61" s="9" t="inlineStr">
         <is>
           <t>6205300000</t>
         </is>
       </c>
-      <c r="C61" s="15" t="n">
+      <c r="C61" s="1" t="n">
         <v>165</v>
       </c>
-      <c r="D61" s="17" t="n">
+      <c r="D61" s="10" t="n">
         <v>30.97</v>
       </c>
-      <c r="E61" s="17" t="n">
+      <c r="E61" s="10" t="n">
         <v>32.32</v>
       </c>
-      <c r="F61" s="17" t="n">
+      <c r="F61" s="10" t="n">
         <v>584.58</v>
       </c>
-      <c r="G61" s="15" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="H61" s="15" t="inlineStr">
+      <c r="G61" s="1" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H61" s="1" t="inlineStr">
         <is>
           <t>PCS</t>
         </is>
@@ -4000,12 +3991,12 @@
           <t>koszula</t>
         </is>
       </c>
-      <c r="J61" s="15" t="inlineStr">
-        <is>
-          <t>CN</t>
-        </is>
-      </c>
-      <c r="K61" s="15" t="inlineStr">
+      <c r="J61" s="1" t="inlineStr">
+        <is>
+          <t>CN</t>
+        </is>
+      </c>
+      <c r="K61" s="1" t="inlineStr">
         <is>
           <t>100</t>
         </is>
@@ -4015,32 +4006,32 @@
       <c r="N61" s="5" t="n"/>
     </row>
     <row r="62">
-      <c r="A62" s="15" t="n">
+      <c r="A62" s="1" t="n">
         <v>61</v>
       </c>
-      <c r="B62" s="18" t="inlineStr">
+      <c r="B62" s="9" t="inlineStr">
         <is>
           <t>6203429000</t>
         </is>
       </c>
-      <c r="C62" s="15" t="n">
+      <c r="C62" s="1" t="n">
         <v>22</v>
       </c>
-      <c r="D62" s="17" t="n">
+      <c r="D62" s="10" t="n">
         <v>6.94</v>
       </c>
-      <c r="E62" s="17" t="n">
+      <c r="E62" s="10" t="n">
         <v>7.314</v>
       </c>
-      <c r="F62" s="17" t="n">
+      <c r="F62" s="10" t="n">
         <v>98.79000000000001</v>
       </c>
-      <c r="G62" s="15" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="H62" s="15" t="inlineStr">
+      <c r="G62" s="1" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H62" s="1" t="inlineStr">
         <is>
           <t>PCS</t>
         </is>
@@ -4050,12 +4041,12 @@
           <t>spodenki</t>
         </is>
       </c>
-      <c r="J62" s="15" t="inlineStr">
-        <is>
-          <t>CN</t>
-        </is>
-      </c>
-      <c r="K62" s="15" t="inlineStr">
+      <c r="J62" s="1" t="inlineStr">
+        <is>
+          <t>CN</t>
+        </is>
+      </c>
+      <c r="K62" s="1" t="inlineStr">
         <is>
           <t>100</t>
         </is>
@@ -4065,32 +4056,32 @@
       <c r="N62" s="5" t="n"/>
     </row>
     <row r="63">
-      <c r="A63" s="15" t="n">
+      <c r="A63" s="1" t="n">
         <v>62</v>
       </c>
-      <c r="B63" s="18" t="inlineStr">
+      <c r="B63" s="9" t="inlineStr">
         <is>
           <t>6203423500</t>
         </is>
       </c>
-      <c r="C63" s="15" t="n">
+      <c r="C63" s="1" t="n">
         <v>57</v>
       </c>
-      <c r="D63" s="17" t="n">
+      <c r="D63" s="10" t="n">
         <v>15.81</v>
       </c>
-      <c r="E63" s="17" t="n">
+      <c r="E63" s="10" t="n">
         <v>16.786</v>
       </c>
-      <c r="F63" s="17" t="n">
+      <c r="F63" s="10" t="n">
         <v>222.84</v>
       </c>
-      <c r="G63" s="15" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="H63" s="15" t="inlineStr">
+      <c r="G63" s="1" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H63" s="1" t="inlineStr">
         <is>
           <t>PCS</t>
         </is>
@@ -4100,12 +4091,12 @@
           <t>spodnie</t>
         </is>
       </c>
-      <c r="J63" s="15" t="inlineStr">
-        <is>
-          <t>CN</t>
-        </is>
-      </c>
-      <c r="K63" s="15" t="inlineStr">
+      <c r="J63" s="1" t="inlineStr">
+        <is>
+          <t>CN</t>
+        </is>
+      </c>
+      <c r="K63" s="1" t="inlineStr">
         <is>
           <t>100</t>
         </is>
@@ -4115,32 +4106,32 @@
       <c r="N63" s="5" t="n"/>
     </row>
     <row r="64">
-      <c r="A64" s="15" t="n">
+      <c r="A64" s="1" t="n">
         <v>63</v>
       </c>
-      <c r="B64" s="18" t="inlineStr">
+      <c r="B64" s="9" t="inlineStr">
         <is>
           <t>6203431900</t>
         </is>
       </c>
-      <c r="C64" s="15" t="n">
+      <c r="C64" s="1" t="n">
         <v>56</v>
       </c>
-      <c r="D64" s="17" t="n">
+      <c r="D64" s="10" t="n">
         <v>19.667</v>
       </c>
-      <c r="E64" s="17" t="n">
+      <c r="E64" s="10" t="n">
         <v>20.555</v>
       </c>
-      <c r="F64" s="17" t="n">
+      <c r="F64" s="10" t="n">
         <v>239.19</v>
       </c>
-      <c r="G64" s="15" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="H64" s="15" t="inlineStr">
+      <c r="G64" s="1" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H64" s="1" t="inlineStr">
         <is>
           <t>PCS</t>
         </is>
@@ -4150,12 +4141,12 @@
           <t>spodnie</t>
         </is>
       </c>
-      <c r="J64" s="15" t="inlineStr">
-        <is>
-          <t>CN</t>
-        </is>
-      </c>
-      <c r="K64" s="15" t="inlineStr">
+      <c r="J64" s="1" t="inlineStr">
+        <is>
+          <t>CN</t>
+        </is>
+      </c>
+      <c r="K64" s="1" t="inlineStr">
         <is>
           <t>100</t>
         </is>
@@ -4165,32 +4156,32 @@
       <c r="N64" s="5" t="n"/>
     </row>
     <row r="65">
-      <c r="A65" s="15" t="n">
+      <c r="A65" s="1" t="n">
         <v>64</v>
       </c>
-      <c r="B65" s="18" t="inlineStr">
+      <c r="B65" s="9" t="inlineStr">
         <is>
           <t>6115969900</t>
         </is>
       </c>
-      <c r="C65" s="15" t="n">
+      <c r="C65" s="1" t="n">
         <v>229</v>
       </c>
-      <c r="D65" s="17" t="n">
+      <c r="D65" s="10" t="n">
         <v>37.06</v>
       </c>
-      <c r="E65" s="17" t="n">
+      <c r="E65" s="10" t="n">
         <v>39.76</v>
       </c>
-      <c r="F65" s="17" t="n">
+      <c r="F65" s="10" t="n">
         <v>392.7</v>
       </c>
-      <c r="G65" s="15" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="H65" s="15" t="inlineStr">
+      <c r="G65" s="1" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H65" s="1" t="inlineStr">
         <is>
           <t>PCS</t>
         </is>
@@ -4200,12 +4191,12 @@
           <t>skarpetki</t>
         </is>
       </c>
-      <c r="J65" s="15" t="inlineStr">
-        <is>
-          <t>CN</t>
-        </is>
-      </c>
-      <c r="K65" s="15" t="inlineStr">
+      <c r="J65" s="1" t="inlineStr">
+        <is>
+          <t>CN</t>
+        </is>
+      </c>
+      <c r="K65" s="1" t="inlineStr">
         <is>
           <t>100</t>
         </is>
@@ -4215,32 +4206,32 @@
       <c r="N65" s="5" t="n"/>
     </row>
     <row r="66">
-      <c r="A66" s="15" t="n">
+      <c r="A66" s="1" t="n">
         <v>65</v>
       </c>
-      <c r="B66" s="18" t="inlineStr">
+      <c r="B66" s="9" t="inlineStr">
         <is>
           <t>6208220000</t>
         </is>
       </c>
-      <c r="C66" s="15" t="n">
+      <c r="C66" s="1" t="n">
         <v>172</v>
       </c>
-      <c r="D66" s="17" t="n">
+      <c r="D66" s="10" t="n">
         <v>33.26</v>
       </c>
-      <c r="E66" s="17" t="n">
+      <c r="E66" s="10" t="n">
         <v>34.61</v>
       </c>
-      <c r="F66" s="17" t="n">
+      <c r="F66" s="10" t="n">
         <v>569.87</v>
       </c>
-      <c r="G66" s="15" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="H66" s="15" t="inlineStr">
+      <c r="G66" s="1" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H66" s="1" t="inlineStr">
         <is>
           <t>PCS</t>
         </is>
@@ -4250,12 +4241,12 @@
           <t>sukienka</t>
         </is>
       </c>
-      <c r="J66" s="15" t="inlineStr">
-        <is>
-          <t>CN</t>
-        </is>
-      </c>
-      <c r="K66" s="15" t="inlineStr">
+      <c r="J66" s="1" t="inlineStr">
+        <is>
+          <t>CN</t>
+        </is>
+      </c>
+      <c r="K66" s="1" t="inlineStr">
         <is>
           <t>100</t>
         </is>
@@ -4774,7 +4765,7 @@
       <c r="M83" s="5" t="n"/>
       <c r="N83" s="5" t="n"/>
     </row>
-    <row r="84">
+    <row r="84" customFormat="1" s="4">
       <c r="A84" s="1" t="n">
         <v>19</v>
       </c>
@@ -5000,7 +4991,7 @@
           <t>EUR</t>
         </is>
       </c>
-      <c r="H91" s="19" t="n"/>
+      <c r="H91" s="16" t="n"/>
       <c r="I91" s="7" t="n"/>
       <c r="J91" s="1" t="inlineStr">
         <is>
@@ -5030,7 +5021,7 @@
           <t>EUR</t>
         </is>
       </c>
-      <c r="H92" s="19" t="n"/>
+      <c r="H92" s="16" t="n"/>
       <c r="I92" s="7" t="n"/>
       <c r="J92" s="1" t="inlineStr">
         <is>
@@ -5060,7 +5051,7 @@
           <t>EUR</t>
         </is>
       </c>
-      <c r="H93" s="19" t="n"/>
+      <c r="H93" s="16" t="n"/>
       <c r="I93" s="7" t="n"/>
       <c r="J93" s="1" t="inlineStr">
         <is>
@@ -5090,7 +5081,7 @@
           <t>EUR</t>
         </is>
       </c>
-      <c r="H94" s="19" t="n"/>
+      <c r="H94" s="16" t="n"/>
       <c r="I94" s="7" t="n"/>
       <c r="J94" s="1" t="inlineStr">
         <is>
@@ -5120,7 +5111,7 @@
           <t>EUR</t>
         </is>
       </c>
-      <c r="H95" s="19" t="n"/>
+      <c r="H95" s="16" t="n"/>
       <c r="I95" s="7" t="n"/>
       <c r="J95" s="1" t="inlineStr">
         <is>
@@ -5150,7 +5141,7 @@
           <t>EUR</t>
         </is>
       </c>
-      <c r="H96" s="19" t="n"/>
+      <c r="H96" s="16" t="n"/>
       <c r="I96" s="7" t="n"/>
       <c r="J96" s="1" t="inlineStr">
         <is>
@@ -5180,7 +5171,7 @@
           <t>EUR</t>
         </is>
       </c>
-      <c r="H97" s="19" t="n"/>
+      <c r="H97" s="16" t="n"/>
       <c r="I97" s="7" t="n"/>
       <c r="J97" s="1" t="inlineStr">
         <is>
@@ -5240,7 +5231,7 @@
           <t>EUR</t>
         </is>
       </c>
-      <c r="H99" s="19" t="n"/>
+      <c r="H99" s="16" t="n"/>
       <c r="I99" s="7" t="n"/>
       <c r="J99" s="1" t="inlineStr">
         <is>
@@ -5270,7 +5261,7 @@
           <t>EUR</t>
         </is>
       </c>
-      <c r="H100" s="19" t="n"/>
+      <c r="H100" s="16" t="n"/>
       <c r="I100" s="7" t="n"/>
       <c r="J100" s="1" t="inlineStr">
         <is>
@@ -5300,7 +5291,7 @@
           <t>EUR</t>
         </is>
       </c>
-      <c r="H101" s="19" t="n"/>
+      <c r="H101" s="16" t="n"/>
       <c r="I101" s="7" t="n"/>
       <c r="J101" s="1" t="inlineStr">
         <is>
@@ -5330,7 +5321,7 @@
           <t>EUR</t>
         </is>
       </c>
-      <c r="H102" s="19" t="n"/>
+      <c r="H102" s="16" t="n"/>
       <c r="I102" s="7" t="n"/>
       <c r="J102" s="1" t="inlineStr">
         <is>
@@ -5360,7 +5351,7 @@
           <t>EUR</t>
         </is>
       </c>
-      <c r="H103" s="19" t="n"/>
+      <c r="H103" s="16" t="n"/>
       <c r="I103" s="7" t="n"/>
       <c r="J103" s="1" t="inlineStr">
         <is>
@@ -5450,7 +5441,7 @@
           <t>EUR</t>
         </is>
       </c>
-      <c r="H106" s="19" t="n"/>
+      <c r="H106" s="16" t="n"/>
       <c r="I106" s="7" t="n"/>
       <c r="J106" s="1" t="inlineStr">
         <is>
@@ -5510,7 +5501,7 @@
           <t>EUR</t>
         </is>
       </c>
-      <c r="H108" s="19" t="n"/>
+      <c r="H108" s="16" t="n"/>
       <c r="I108" s="7" t="n"/>
       <c r="J108" s="1" t="inlineStr">
         <is>
@@ -5570,7 +5561,7 @@
           <t>EUR</t>
         </is>
       </c>
-      <c r="H110" s="19" t="n"/>
+      <c r="H110" s="16" t="n"/>
       <c r="I110" s="7" t="n"/>
       <c r="J110" s="1" t="inlineStr">
         <is>
@@ -5717,7 +5708,7 @@
           <t>EUR</t>
         </is>
       </c>
-      <c r="H115" s="19" t="n"/>
+      <c r="H115" s="16" t="n"/>
       <c r="I115" s="7" t="n"/>
       <c r="J115" s="1" t="inlineStr">
         <is>
@@ -5771,7 +5762,7 @@
           <t>EUR</t>
         </is>
       </c>
-      <c r="H117" s="19" t="n"/>
+      <c r="H117" s="16" t="n"/>
       <c r="I117" s="7" t="n"/>
       <c r="J117" s="1" t="inlineStr">
         <is>
@@ -5825,7 +5816,7 @@
           <t>EUR</t>
         </is>
       </c>
-      <c r="H119" s="19" t="n"/>
+      <c r="H119" s="16" t="n"/>
       <c r="I119" s="7" t="n"/>
       <c r="J119" s="1" t="inlineStr">
         <is>
@@ -5879,7 +5870,7 @@
           <t>EUR</t>
         </is>
       </c>
-      <c r="H121" s="19" t="n"/>
+      <c r="H121" s="16" t="n"/>
       <c r="I121" s="7" t="n"/>
       <c r="J121" s="1" t="inlineStr">
         <is>
@@ -5933,7 +5924,7 @@
           <t>EUR</t>
         </is>
       </c>
-      <c r="H123" s="19" t="n"/>
+      <c r="H123" s="16" t="n"/>
       <c r="I123" s="7" t="n"/>
       <c r="J123" s="1" t="inlineStr">
         <is>
@@ -5987,7 +5978,7 @@
           <t>EUR</t>
         </is>
       </c>
-      <c r="H125" s="19" t="n"/>
+      <c r="H125" s="16" t="n"/>
       <c r="I125" s="7" t="n"/>
       <c r="J125" s="1" t="inlineStr">
         <is>
@@ -6041,7 +6032,7 @@
           <t>EUR</t>
         </is>
       </c>
-      <c r="H127" s="19" t="n"/>
+      <c r="H127" s="16" t="n"/>
       <c r="I127" s="7" t="n"/>
       <c r="J127" s="1" t="inlineStr">
         <is>
@@ -6095,7 +6086,7 @@
           <t>EUR</t>
         </is>
       </c>
-      <c r="H129" s="19" t="n"/>
+      <c r="H129" s="16" t="n"/>
       <c r="I129" s="7" t="n"/>
       <c r="J129" s="1" t="inlineStr">
         <is>
@@ -6149,7 +6140,7 @@
           <t>EUR</t>
         </is>
       </c>
-      <c r="H131" s="19" t="n"/>
+      <c r="H131" s="16" t="n"/>
       <c r="I131" s="7" t="n"/>
       <c r="J131" s="1" t="inlineStr">
         <is>
@@ -6203,7 +6194,7 @@
           <t>EUR</t>
         </is>
       </c>
-      <c r="H133" s="19" t="n"/>
+      <c r="H133" s="16" t="n"/>
       <c r="I133" s="7" t="n"/>
       <c r="J133" s="1" t="inlineStr">
         <is>
